--- a/成果.xlsx
+++ b/成果.xlsx
@@ -8,12 +8,13 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Users\peggy\Github\ShijingNature\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{53542B4F-E0AE-4D6C-A4CA-1097E5FCCFDF}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4B583E64-38B0-4939-B19C-6E8F4B3744F5}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView minimized="1" xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12645" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12645" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="工作表1" sheetId="1" r:id="rId1"/>
+    <sheet name="工作表2" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -25,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="309" uniqueCount="79">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="457" uniqueCount="87">
   <si>
     <t>愛情</t>
   </si>
@@ -289,13 +290,118 @@
   </si>
   <si>
     <t>其他</t>
+  </si>
+  <si>
+    <t>兩棲</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Z</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>物色類別</t>
+  </si>
+  <si>
+    <r>
+      <t>詞彙頻次</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color rgb="FFFFFFFF"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>(</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color rgb="FFFFFFFF"/>
+        <rFont val="標楷體"/>
+        <family val="4"/>
+        <charset val="136"/>
+      </rPr>
+      <t>次</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color rgb="FFFFFFFF"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>相對頻率</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color rgb="FFFFFFFF"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>(%)</t>
+    </r>
+  </si>
+  <si>
+    <t>兩棲</t>
+  </si>
+  <si>
+    <r>
+      <t>觀察次數</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color rgb="FFFFFFFF"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>(</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color rgb="FFFFFFFF"/>
+        <rFont val="標楷體"/>
+        <family val="4"/>
+        <charset val="136"/>
+      </rPr>
+      <t>次</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color rgb="FFFFFFFF"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>)</t>
+    </r>
+  </si>
+  <si>
+    <t>穀物</t>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="9" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -325,8 +431,42 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="標楷體"/>
+      <family val="4"/>
+      <charset val="136"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color rgb="FF000000"/>
+      <name val="標楷體"/>
+      <family val="4"/>
+      <charset val="136"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color rgb="FF000000"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+    </font>
   </fonts>
-  <fills count="3">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -339,8 +479,20 @@
         <bgColor theme="4"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF5B9BD5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDDEBF7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="3">
+  <borders count="9">
     <border>
       <left/>
       <right/>
@@ -372,6 +524,74 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="medium">
+        <color rgb="FF9BC2E6"/>
+      </left>
+      <right/>
+      <top style="medium">
+        <color rgb="FF9BC2E6"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="FF9BC2E6"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="medium">
+        <color rgb="FF9BC2E6"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="FF9BC2E6"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color rgb="FF9BC2E6"/>
+      </right>
+      <top style="medium">
+        <color rgb="FF9BC2E6"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="FF9BC2E6"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="FF9BC2E6"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color rgb="FF9BC2E6"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color rgb="FF9BC2E6"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color rgb="FF9BC2E6"/>
+      </right>
+      <top/>
+      <bottom style="medium">
+        <color rgb="FF9BC2E6"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
@@ -379,7 +599,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="29">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -389,12 +609,87 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="10" fontId="8" fillId="4" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="10" fontId="8" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="justify" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="8" fillId="4" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="8" fillId="4" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="8" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="8" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="一般" xfId="0" builtinId="0"/>
     <cellStyle name="百分比" xfId="1" builtinId="5"/>
   </cellStyles>
-  <dxfs count="28">
+  <dxfs count="31">
+    <dxf>
+      <numFmt numFmtId="2" formatCode="0.00"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="2" formatCode="0.00"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="2" formatCode="0.00"/>
+    </dxf>
     <dxf>
       <numFmt numFmtId="2" formatCode="0.00"/>
     </dxf>
@@ -1011,7 +1306,7 @@
                   <c:v>20</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>2</c:v>
+                  <c:v>5</c:v>
                 </c:pt>
                 <c:pt idx="4">
                   <c:v>28</c:v>
@@ -1094,7 +1389,7 @@
                   <c:v>16</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>51</c:v>
+                  <c:v>55</c:v>
                 </c:pt>
                 <c:pt idx="4">
                   <c:v>4</c:v>
@@ -1978,8 +2273,10 @@
   <autoFilter ref="A23:C30" xr:uid="{9C8B6933-EDDA-493F-AE4D-50AD291B5EC6}"/>
   <tableColumns count="3">
     <tableColumn id="1" xr3:uid="{1ED248EF-F553-4840-853A-47EC0AE5BE18}" name="欄1"/>
-    <tableColumn id="2" xr3:uid="{AF4D279C-16B8-4423-8F0E-725B2FB74AA4}" name="詞彙頻次(次)"/>
-    <tableColumn id="3" xr3:uid="{1312C3BB-F1D1-4189-A147-EC460D937304}" name="相對頻率(%)" dataDxfId="27" dataCellStyle="百分比">
+    <tableColumn id="2" xr3:uid="{AF4D279C-16B8-4423-8F0E-725B2FB74AA4}" name="詞彙頻次(次)">
+      <calculatedColumnFormula>I2</calculatedColumnFormula>
+    </tableColumn>
+    <tableColumn id="3" xr3:uid="{1312C3BB-F1D1-4189-A147-EC460D937304}" name="相對頻率(%)" dataDxfId="30" dataCellStyle="百分比">
       <calculatedColumnFormula>B24/$B$32</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -1988,14 +2285,14 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{B915F2C6-D85D-4C09-90FB-9C202E56150F}" name="表格2" displayName="表格2" ref="F23:J43" totalsRowShown="0" headerRowDxfId="20" dataDxfId="21">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{B915F2C6-D85D-4C09-90FB-9C202E56150F}" name="表格2" displayName="表格2" ref="F23:J43" totalsRowShown="0" headerRowDxfId="29" dataDxfId="28">
   <autoFilter ref="F23:J43" xr:uid="{C1830A39-9D9C-4255-B963-DF93DD17792A}"/>
   <tableColumns count="5">
-    <tableColumn id="1" xr3:uid="{D0EAF4BA-63C3-44DD-B571-892C51D5AF0E}" name="排名" dataDxfId="26"/>
-    <tableColumn id="2" xr3:uid="{9E780C5B-D021-4271-8C6D-4051D4221A60}" name="詞彙" dataDxfId="25"/>
-    <tableColumn id="3" xr3:uid="{554F87E5-2979-4F4E-9FBF-60D2CA39534D}" name="總頻次" dataDxfId="24"/>
-    <tableColumn id="4" xr3:uid="{B21E237B-15F2-4FA3-B450-6235D7B51FA2}" name="相對頻率(%)" dataDxfId="23"/>
-    <tableColumn id="5" xr3:uid="{3E3D91B9-4A86-4EDC-AC5E-321D5EE3B926}" name="意象大類" dataDxfId="22"/>
+    <tableColumn id="1" xr3:uid="{D0EAF4BA-63C3-44DD-B571-892C51D5AF0E}" name="排名" dataDxfId="27"/>
+    <tableColumn id="2" xr3:uid="{9E780C5B-D021-4271-8C6D-4051D4221A60}" name="詞彙" dataDxfId="26"/>
+    <tableColumn id="3" xr3:uid="{554F87E5-2979-4F4E-9FBF-60D2CA39534D}" name="總頻次" dataDxfId="25"/>
+    <tableColumn id="4" xr3:uid="{B21E237B-15F2-4FA3-B450-6235D7B51FA2}" name="相對頻率(%)" dataDxfId="24"/>
+    <tableColumn id="5" xr3:uid="{3E3D91B9-4A86-4EDC-AC5E-321D5EE3B926}" name="意象大類" dataDxfId="23"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -2007,7 +2304,7 @@
   <tableColumns count="3">
     <tableColumn id="1" xr3:uid="{5D2BEBA4-48AE-49E9-A740-2CD1D7A5D97C}" name="植物意象"/>
     <tableColumn id="2" xr3:uid="{810ABC46-33C5-4F47-B09A-C31C27D243EB}" name="詞彙頻次(次)"/>
-    <tableColumn id="3" xr3:uid="{C441E861-4ED4-4EC9-B22D-6457974285AE}" name="相對頻率(%)" dataDxfId="19" dataCellStyle="百分比">
+    <tableColumn id="3" xr3:uid="{C441E861-4ED4-4EC9-B22D-6457974285AE}" name="相對頻率(%)" dataDxfId="22" dataCellStyle="百分比">
       <calculatedColumnFormula>N24/$N$30</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -2021,7 +2318,7 @@
   <tableColumns count="3">
     <tableColumn id="1" xr3:uid="{2BB23CE7-8A91-447D-B869-C39CB7C6045F}" name="動物意象"/>
     <tableColumn id="2" xr3:uid="{AA5286D7-AD6B-49E8-8216-B711C928EE27}" name="詞彙頻次(次)"/>
-    <tableColumn id="3" xr3:uid="{31CA02D8-1B31-4AD1-9C7F-9B7E1AC0636B}" name="相對頻率(%)" dataDxfId="18" dataCellStyle="百分比">
+    <tableColumn id="3" xr3:uid="{31CA02D8-1B31-4AD1-9C7F-9B7E1AC0636B}" name="相對頻率(%)" dataDxfId="21" dataCellStyle="百分比">
       <calculatedColumnFormula>S24/$S$31</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -2047,48 +2344,51 @@
 </file>
 
 <file path=xl/tables/table6.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="8" xr:uid="{BA7026CB-EABB-4AB8-9E5F-FBA172C5BA78}" name="表格8" displayName="表格8" ref="A71:G78" totalsRowShown="0">
-  <autoFilter ref="A71:G78" xr:uid="{7DA71F53-113D-4DD3-9541-1E38846ED451}"/>
-  <tableColumns count="7">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="8" xr:uid="{BA7026CB-EABB-4AB8-9E5F-FBA172C5BA78}" name="表格8" displayName="表格8" ref="A71:H78" totalsRowShown="0">
+  <autoFilter ref="A71:H78" xr:uid="{7DA71F53-113D-4DD3-9541-1E38846ED451}"/>
+  <tableColumns count="8">
     <tableColumn id="1" xr3:uid="{2B8B62BA-F3B0-4D41-BF5F-09BF2492A801}" name="標準化殘差"/>
-    <tableColumn id="2" xr3:uid="{0C34C15A-AF50-4034-9357-7654F9AD7130}" name="愛情" dataDxfId="17"/>
-    <tableColumn id="3" xr3:uid="{FB7306F1-B9C4-4A38-A840-B5F672D02BD7}" name="婚姻" dataDxfId="16"/>
-    <tableColumn id="4" xr3:uid="{141ABAE6-8176-4AE0-8319-090AAD322B74}" name="征人差役" dataDxfId="15"/>
-    <tableColumn id="5" xr3:uid="{86348135-5641-40BD-B42E-31AEDB87A017}" name="勞作生活" dataDxfId="14"/>
-    <tableColumn id="6" xr3:uid="{1E8729AA-7F1E-4890-BF76-936203572833}" name="社會政治" dataDxfId="13"/>
-    <tableColumn id="7" xr3:uid="{114C20CC-8BA3-41A9-A97D-BA76CB48BE09}" name="感懷" dataDxfId="12"/>
+    <tableColumn id="2" xr3:uid="{0C34C15A-AF50-4034-9357-7654F9AD7130}" name="Z" dataDxfId="20"/>
+    <tableColumn id="3" xr3:uid="{FB7306F1-B9C4-4A38-A840-B5F672D02BD7}" name="愛情" dataDxfId="19"/>
+    <tableColumn id="4" xr3:uid="{141ABAE6-8176-4AE0-8319-090AAD322B74}" name="婚姻" dataDxfId="18"/>
+    <tableColumn id="5" xr3:uid="{86348135-5641-40BD-B42E-31AEDB87A017}" name="征人差役" dataDxfId="17"/>
+    <tableColumn id="6" xr3:uid="{1E8729AA-7F1E-4890-BF76-936203572833}" name="勞作生活" dataDxfId="16"/>
+    <tableColumn id="7" xr3:uid="{114C20CC-8BA3-41A9-A97D-BA76CB48BE09}" name="社會政治" dataDxfId="15"/>
+    <tableColumn id="8" xr3:uid="{089AB8B7-78C8-43D2-A78C-0E43D03BDF44}" name="感懷" dataDxfId="14"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table7.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="9" xr:uid="{6ABF1C21-9707-49F7-8AAF-3A809B95F1E6}" name="表格9" displayName="表格9" ref="A102:G107" totalsRowShown="0">
-  <autoFilter ref="A102:G107" xr:uid="{89010BCE-0E77-48D9-BFBF-80D4283829E0}"/>
-  <tableColumns count="7">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="9" xr:uid="{6ABF1C21-9707-49F7-8AAF-3A809B95F1E6}" name="表格9" displayName="表格9" ref="A102:H107" totalsRowShown="0">
+  <autoFilter ref="A102:H107" xr:uid="{89010BCE-0E77-48D9-BFBF-80D4283829E0}"/>
+  <tableColumns count="8">
     <tableColumn id="1" xr3:uid="{390BC721-B34F-4738-8251-129D58177A45}" name="標準化殘差"/>
-    <tableColumn id="2" xr3:uid="{6535902F-E5FC-4B29-828B-E3272F0CCDA6}" name="愛情" dataDxfId="11"/>
-    <tableColumn id="3" xr3:uid="{2E1CD68A-FF8F-46D8-9C6D-3BD1917E97FF}" name="婚姻" dataDxfId="10"/>
-    <tableColumn id="4" xr3:uid="{098BE160-F55E-4CD0-9420-8F6169EE81C0}" name="征人差役" dataDxfId="9"/>
-    <tableColumn id="5" xr3:uid="{FB871EF2-8638-4C58-A315-280626600862}" name="勞作生活" dataDxfId="8"/>
-    <tableColumn id="6" xr3:uid="{7CD3D22D-9506-4974-995C-059B8F4AC2BD}" name="社會政治" dataDxfId="7"/>
-    <tableColumn id="7" xr3:uid="{3CC3DB54-566C-42EF-B5ED-A9B3C28C23AB}" name="感懷" dataDxfId="6"/>
+    <tableColumn id="2" xr3:uid="{6535902F-E5FC-4B29-828B-E3272F0CCDA6}" name="Z" dataDxfId="13"/>
+    <tableColumn id="3" xr3:uid="{2E1CD68A-FF8F-46D8-9C6D-3BD1917E97FF}" name="愛情" dataDxfId="12"/>
+    <tableColumn id="4" xr3:uid="{098BE160-F55E-4CD0-9420-8F6169EE81C0}" name="婚姻" dataDxfId="11"/>
+    <tableColumn id="5" xr3:uid="{FB871EF2-8638-4C58-A315-280626600862}" name="征人差役" dataDxfId="10"/>
+    <tableColumn id="6" xr3:uid="{7CD3D22D-9506-4974-995C-059B8F4AC2BD}" name="勞作生活" dataDxfId="9"/>
+    <tableColumn id="7" xr3:uid="{3CC3DB54-566C-42EF-B5ED-A9B3C28C23AB}" name="社會政治" dataDxfId="8"/>
+    <tableColumn id="8" xr3:uid="{840F3291-6FBC-445E-A360-B3038DCE0FB8}" name="感懷" dataDxfId="7"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table8.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="10" xr:uid="{F2DE0C51-2A4B-4558-9F94-A812C7C77A31}" name="表格10" displayName="表格10" ref="A132:G138" totalsRowShown="0">
-  <autoFilter ref="A132:G138" xr:uid="{9025916F-BB8F-48D3-9739-C0B41289B7F9}"/>
-  <tableColumns count="7">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="10" xr:uid="{F2DE0C51-2A4B-4558-9F94-A812C7C77A31}" name="表格10" displayName="表格10" ref="A132:H138" totalsRowShown="0">
+  <autoFilter ref="A132:H138" xr:uid="{9025916F-BB8F-48D3-9739-C0B41289B7F9}"/>
+  <tableColumns count="8">
     <tableColumn id="1" xr3:uid="{BD8AE72E-8DBE-472A-B861-D0953ED88522}" name="標準化殘差"/>
-    <tableColumn id="2" xr3:uid="{62860CA7-46BA-4D99-940D-63A71C3EA2E3}" name="愛情" dataDxfId="5"/>
-    <tableColumn id="3" xr3:uid="{ECF707A9-55F6-4942-B843-50F2E0368EDD}" name="婚姻" dataDxfId="4"/>
-    <tableColumn id="4" xr3:uid="{C0BA2D68-6F21-4561-97EA-324125D8B33D}" name="征人差役" dataDxfId="3"/>
-    <tableColumn id="5" xr3:uid="{05BE0D92-D869-4EC8-B3E8-F1A1CF35DFA7}" name="勞作生活" dataDxfId="2"/>
-    <tableColumn id="6" xr3:uid="{75168639-B0AD-4FC9-ACCB-B0E17F62BDC7}" name="社會政治" dataDxfId="1"/>
-    <tableColumn id="7" xr3:uid="{DA0050F6-90C0-4647-A1C4-E48B520D5BE5}" name="感懷" dataDxfId="0"/>
+    <tableColumn id="2" xr3:uid="{62860CA7-46BA-4D99-940D-63A71C3EA2E3}" name="Z" dataDxfId="6"/>
+    <tableColumn id="3" xr3:uid="{ECF707A9-55F6-4942-B843-50F2E0368EDD}" name="愛情" dataDxfId="5"/>
+    <tableColumn id="4" xr3:uid="{C0BA2D68-6F21-4561-97EA-324125D8B33D}" name="婚姻" dataDxfId="4"/>
+    <tableColumn id="5" xr3:uid="{05BE0D92-D869-4EC8-B3E8-F1A1CF35DFA7}" name="征人差役" dataDxfId="3"/>
+    <tableColumn id="6" xr3:uid="{75168639-B0AD-4FC9-ACCB-B0E17F62BDC7}" name="勞作生活" dataDxfId="2"/>
+    <tableColumn id="7" xr3:uid="{DA0050F6-90C0-4647-A1C4-E48B520D5BE5}" name="社會政治" dataDxfId="1"/>
+    <tableColumn id="8" xr3:uid="{B9E65ECE-CEA0-44D4-B49F-45D34984C21C}" name="感懷" dataDxfId="0"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -2522,7 +2822,7 @@
         <v>20</v>
       </c>
       <c r="E6">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="F6">
         <v>28</v>
@@ -2532,7 +2832,7 @@
       </c>
       <c r="I6">
         <f t="shared" si="0"/>
-        <v>128</v>
+        <v>131</v>
       </c>
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.25">
@@ -2549,7 +2849,7 @@
         <v>16</v>
       </c>
       <c r="E7">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="F7">
         <v>4</v>
@@ -2558,8 +2858,8 @@
         <v>2</v>
       </c>
       <c r="I7">
-        <f t="shared" si="0"/>
-        <v>110</v>
+        <f>SUM(B7:G7)</f>
+        <v>114</v>
       </c>
     </row>
     <row r="8" spans="1:9" x14ac:dyDescent="0.25">
@@ -2592,7 +2892,7 @@
     <row r="11" spans="1:9" x14ac:dyDescent="0.25">
       <c r="I11">
         <f>SUM(I2:I8)</f>
-        <v>1260</v>
+        <v>1267</v>
       </c>
     </row>
     <row r="23" spans="1:20" x14ac:dyDescent="0.25">
@@ -2644,11 +2944,12 @@
         <v>4</v>
       </c>
       <c r="B24">
+        <f>I2</f>
         <v>118</v>
       </c>
       <c r="C24" s="1">
         <f>B24/$B$32</f>
-        <v>9.3650793650793651E-2</v>
+        <v>9.3133385951065503E-2</v>
       </c>
       <c r="F24" s="5">
         <v>1</v>
@@ -2691,11 +2992,12 @@
         <v>5</v>
       </c>
       <c r="B25">
+        <f t="shared" ref="B25:B30" si="1">I3</f>
         <v>349</v>
       </c>
       <c r="C25" s="1">
-        <f t="shared" ref="C25:C30" si="1">B25/$B$32</f>
-        <v>0.276984126984127</v>
+        <f t="shared" ref="C25:C30" si="2">B25/$B$32</f>
+        <v>0.27545382794001577</v>
       </c>
       <c r="F25" s="5">
         <v>2</v>
@@ -2719,7 +3021,7 @@
         <v>112</v>
       </c>
       <c r="O25" s="1">
-        <f t="shared" ref="O25:O28" si="2">N25/$N$30</f>
+        <f t="shared" ref="O25:O28" si="3">N25/$N$30</f>
         <v>0.3209169054441261</v>
       </c>
       <c r="R25" t="s">
@@ -2729,7 +3031,7 @@
         <v>71</v>
       </c>
       <c r="T25" s="1">
-        <f t="shared" ref="T25:T29" si="3">S25/$S$31</f>
+        <f t="shared" ref="T25:T29" si="4">S25/$S$31</f>
         <v>0.29831932773109243</v>
       </c>
     </row>
@@ -2738,11 +3040,12 @@
         <v>6</v>
       </c>
       <c r="B26">
+        <f t="shared" si="1"/>
         <v>238</v>
       </c>
       <c r="C26" s="1">
-        <f t="shared" si="1"/>
-        <v>0.18888888888888888</v>
+        <f t="shared" si="2"/>
+        <v>0.18784530386740331</v>
       </c>
       <c r="F26" s="5">
         <v>3</v>
@@ -2766,18 +3069,18 @@
         <v>36</v>
       </c>
       <c r="O26" s="1">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0.10315186246418338</v>
       </c>
       <c r="R26" t="s">
         <v>57</v>
       </c>
       <c r="S26">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="T26" s="1">
-        <f t="shared" si="3"/>
-        <v>8.8235294117647065E-2</v>
+        <f t="shared" si="4"/>
+        <v>0.10084033613445378</v>
       </c>
     </row>
     <row r="27" spans="1:20" x14ac:dyDescent="0.25">
@@ -2785,11 +3088,12 @@
         <v>7</v>
       </c>
       <c r="B27">
+        <f t="shared" si="1"/>
         <v>139</v>
       </c>
       <c r="C27" s="1">
-        <f t="shared" si="1"/>
-        <v>0.11031746031746031</v>
+        <f t="shared" si="2"/>
+        <v>0.10970797158642462</v>
       </c>
       <c r="F27" s="5">
         <v>4</v>
@@ -2813,7 +3117,7 @@
         <v>35</v>
       </c>
       <c r="O27" s="1">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0.10028653295128939</v>
       </c>
       <c r="R27" t="s">
@@ -2823,7 +3127,7 @@
         <v>19</v>
       </c>
       <c r="T27" s="1">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>7.9831932773109238E-2</v>
       </c>
     </row>
@@ -2832,11 +3136,12 @@
         <v>8</v>
       </c>
       <c r="B28">
-        <v>128</v>
+        <f t="shared" si="1"/>
+        <v>131</v>
       </c>
       <c r="C28" s="1">
-        <f t="shared" si="1"/>
-        <v>0.10158730158730159</v>
+        <f t="shared" si="2"/>
+        <v>0.10339384372533544</v>
       </c>
       <c r="F28" s="5">
         <v>5</v>
@@ -2860,7 +3165,7 @@
         <v>23</v>
       </c>
       <c r="O28" s="1">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>6.5902578796561598E-2</v>
       </c>
       <c r="R28" t="s">
@@ -2870,7 +3175,7 @@
         <v>7</v>
       </c>
       <c r="T28" s="1">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>2.9411764705882353E-2</v>
       </c>
     </row>
@@ -2879,11 +3184,12 @@
         <v>9</v>
       </c>
       <c r="B29">
-        <v>110</v>
+        <f t="shared" si="1"/>
+        <v>114</v>
       </c>
       <c r="C29" s="1">
-        <f t="shared" si="1"/>
-        <v>8.7301587301587297E-2</v>
+        <f t="shared" si="2"/>
+        <v>8.9976322020520916E-2</v>
       </c>
       <c r="F29" s="5">
         <v>6</v>
@@ -2901,14 +3207,14 @@
         <v>4</v>
       </c>
       <c r="R29" t="s">
-        <v>59</v>
+        <v>79</v>
       </c>
       <c r="S29">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="T29" s="1">
-        <f t="shared" si="3"/>
-        <v>1.680672268907563E-2</v>
+        <f t="shared" si="4"/>
+        <v>4.2016806722689074E-3</v>
       </c>
     </row>
     <row r="30" spans="1:20" x14ac:dyDescent="0.25">
@@ -2916,11 +3222,12 @@
         <v>10</v>
       </c>
       <c r="B30">
+        <f t="shared" si="1"/>
         <v>178</v>
       </c>
       <c r="C30" s="1">
-        <f t="shared" si="1"/>
-        <v>0.14126984126984127</v>
+        <f t="shared" si="2"/>
+        <v>0.1404893449092344</v>
       </c>
       <c r="F30" s="5">
         <v>7</v>
@@ -2976,7 +3283,7 @@
       </c>
       <c r="B32">
         <f>SUM(B24:B30)</f>
-        <v>1260</v>
+        <v>1267</v>
       </c>
       <c r="C32" s="2">
         <f>SUM(C24:C30)</f>
@@ -3128,7 +3435,7 @@
         <v>10</v>
       </c>
       <c r="T37">
-        <f>SUM(N37:S37)</f>
+        <f t="shared" ref="T37:T43" si="5">SUM(N37:S37)</f>
         <v>118</v>
       </c>
     </row>
@@ -3170,7 +3477,7 @@
         <v>17</v>
       </c>
       <c r="T38">
-        <f>SUM(N38:S38)</f>
+        <f t="shared" si="5"/>
         <v>349</v>
       </c>
     </row>
@@ -3212,7 +3519,7 @@
         <v>7</v>
       </c>
       <c r="T39">
-        <f>SUM(N39:S39)</f>
+        <f t="shared" si="5"/>
         <v>238</v>
       </c>
     </row>
@@ -3254,7 +3561,7 @@
         <v>8</v>
       </c>
       <c r="T40">
-        <f>SUM(N40:S40)</f>
+        <f t="shared" si="5"/>
         <v>139</v>
       </c>
     </row>
@@ -3287,7 +3594,7 @@
         <v>20</v>
       </c>
       <c r="Q41">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="R41">
         <v>28</v>
@@ -3296,8 +3603,8 @@
         <v>9</v>
       </c>
       <c r="T41">
-        <f>SUM(N41:S41)</f>
-        <v>128</v>
+        <f t="shared" si="5"/>
+        <v>131</v>
       </c>
     </row>
     <row r="42" spans="1:20" x14ac:dyDescent="0.25">
@@ -3329,7 +3636,7 @@
         <v>16</v>
       </c>
       <c r="Q42">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="R42">
         <v>4</v>
@@ -3338,8 +3645,8 @@
         <v>2</v>
       </c>
       <c r="T42">
-        <f>SUM(N42:S42)</f>
-        <v>110</v>
+        <f t="shared" si="5"/>
+        <v>114</v>
       </c>
     </row>
     <row r="43" spans="1:20" x14ac:dyDescent="0.25">
@@ -3380,7 +3687,7 @@
         <v>6</v>
       </c>
       <c r="T43">
-        <f>SUM(N43:S43)</f>
+        <f t="shared" si="5"/>
         <v>178</v>
       </c>
     </row>
@@ -3394,28 +3701,28 @@
         <v>350</v>
       </c>
       <c r="O44">
-        <f t="shared" ref="O44:T44" si="4">SUM(O37:O43)</f>
+        <f t="shared" ref="O44:T44" si="6">SUM(O37:O43)</f>
         <v>245</v>
       </c>
       <c r="P44">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>160</v>
       </c>
       <c r="Q44">
-        <f t="shared" si="4"/>
-        <v>209</v>
+        <f t="shared" si="6"/>
+        <v>216</v>
       </c>
       <c r="R44">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>237</v>
       </c>
       <c r="S44">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>59</v>
       </c>
       <c r="T44">
-        <f t="shared" si="4"/>
-        <v>1260</v>
+        <f t="shared" si="6"/>
+        <v>1267</v>
       </c>
     </row>
     <row r="48" spans="1:20" x14ac:dyDescent="0.25">
@@ -3495,27 +3802,27 @@
       </c>
       <c r="K49">
         <f>$H49*B$56/$H$56</f>
-        <v>32.777777777777779</v>
+        <v>32.596685082872931</v>
       </c>
       <c r="L49">
         <f>$H49*C$56/$H$56</f>
-        <v>22.944444444444443</v>
+        <v>22.817679558011051</v>
       </c>
       <c r="M49">
         <f>$H49*D$56/$H$56</f>
-        <v>14.984126984126984</v>
+        <v>14.901341752170481</v>
       </c>
       <c r="N49">
-        <f t="shared" ref="L49:P55" si="5">$H49*E$56/$H$56</f>
-        <v>19.573015873015873</v>
+        <f t="shared" ref="N49:P55" si="7">$H49*E$56/$H$56</f>
+        <v>20.116811365430149</v>
       </c>
       <c r="O49">
-        <f t="shared" si="5"/>
-        <v>22.195238095238096</v>
+        <f t="shared" si="7"/>
+        <v>22.072612470402525</v>
       </c>
       <c r="P49">
-        <f t="shared" si="5"/>
-        <v>5.5253968253968253</v>
+        <f t="shared" si="7"/>
+        <v>5.4948697711128647</v>
       </c>
     </row>
     <row r="50" spans="1:16" x14ac:dyDescent="0.25">
@@ -3548,27 +3855,27 @@
       </c>
       <c r="K50">
         <f>$H50*B$56/$H$56</f>
-        <v>96.944444444444443</v>
+        <v>96.408839779005518</v>
       </c>
       <c r="L50">
-        <f t="shared" ref="L50:L55" si="6">$H50*C$56/$H$56</f>
-        <v>67.861111111111114</v>
+        <f t="shared" ref="L50:L55" si="8">$H50*C$56/$H$56</f>
+        <v>67.486187845303874</v>
       </c>
       <c r="M50">
-        <f t="shared" ref="M50:M55" si="7">$H50*D$56/$H$56</f>
-        <v>44.317460317460316</v>
+        <f t="shared" ref="M50:M55" si="9">$H50*D$56/$H$56</f>
+        <v>44.072612470402525</v>
       </c>
       <c r="N50">
-        <f t="shared" si="5"/>
-        <v>57.889682539682539</v>
+        <f t="shared" si="7"/>
+        <v>59.498026835043412</v>
       </c>
       <c r="O50">
-        <f t="shared" si="5"/>
-        <v>65.645238095238099</v>
+        <f t="shared" si="7"/>
+        <v>65.282557221783748</v>
       </c>
       <c r="P50">
-        <f t="shared" si="5"/>
-        <v>16.342063492063492</v>
+        <f t="shared" si="7"/>
+        <v>16.25177584846093</v>
       </c>
     </row>
     <row r="51" spans="1:16" x14ac:dyDescent="0.25">
@@ -3601,27 +3908,27 @@
       </c>
       <c r="K51">
         <f>$H51*B$56/$H$56</f>
-        <v>66.111111111111114</v>
+        <v>65.745856353591165</v>
       </c>
       <c r="L51">
-        <f t="shared" si="6"/>
-        <v>46.277777777777779</v>
+        <f t="shared" si="8"/>
+        <v>46.02209944751381</v>
       </c>
       <c r="M51">
+        <f t="shared" si="9"/>
+        <v>30.055248618784532</v>
+      </c>
+      <c r="N51">
         <f t="shared" si="7"/>
-        <v>30.222222222222221</v>
-      </c>
-      <c r="N51">
-        <f t="shared" si="5"/>
-        <v>39.477777777777774</v>
+        <v>40.574585635359114</v>
       </c>
       <c r="O51">
-        <f t="shared" si="5"/>
-        <v>44.766666666666666</v>
+        <f t="shared" si="7"/>
+        <v>44.519337016574589</v>
       </c>
       <c r="P51">
-        <f t="shared" si="5"/>
-        <v>11.144444444444444</v>
+        <f t="shared" si="7"/>
+        <v>11.082872928176796</v>
       </c>
     </row>
     <row r="52" spans="1:16" x14ac:dyDescent="0.25">
@@ -3654,27 +3961,27 @@
       </c>
       <c r="K52">
         <f>$H52*B$56/$H$56</f>
-        <v>38.611111111111114</v>
+        <v>38.39779005524862</v>
       </c>
       <c r="L52">
-        <f t="shared" si="6"/>
-        <v>27.027777777777779</v>
+        <f t="shared" si="8"/>
+        <v>26.878453038674031</v>
       </c>
       <c r="M52">
+        <f t="shared" si="9"/>
+        <v>17.55327545382794</v>
+      </c>
+      <c r="N52">
         <f t="shared" si="7"/>
-        <v>17.650793650793652</v>
-      </c>
-      <c r="N52">
-        <f t="shared" si="5"/>
-        <v>23.056349206349207</v>
+        <v>23.696921862667718</v>
       </c>
       <c r="O52">
-        <f t="shared" si="5"/>
-        <v>26.145238095238096</v>
+        <f t="shared" si="7"/>
+        <v>26.000789265982636</v>
       </c>
       <c r="P52">
-        <f t="shared" si="5"/>
-        <v>6.5087301587301587</v>
+        <f t="shared" si="7"/>
+        <v>6.472770323599053</v>
       </c>
     </row>
     <row r="53" spans="1:16" x14ac:dyDescent="0.25">
@@ -3691,7 +3998,7 @@
         <v>20</v>
       </c>
       <c r="E53">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="F53">
         <v>28</v>
@@ -3700,34 +4007,34 @@
         <v>9</v>
       </c>
       <c r="H53">
-        <v>128</v>
+        <v>131</v>
       </c>
       <c r="J53" t="s">
         <v>37</v>
       </c>
       <c r="K53">
-        <f t="shared" ref="K50:K55" si="8">$H53*B$56/$H$56</f>
-        <v>35.555555555555557</v>
+        <f t="shared" ref="K53:K55" si="10">$H53*B$56/$H$56</f>
+        <v>36.187845303867405</v>
       </c>
       <c r="L53">
-        <f t="shared" si="6"/>
-        <v>24.888888888888889</v>
+        <f t="shared" si="8"/>
+        <v>25.331491712707184</v>
       </c>
       <c r="M53">
+        <f t="shared" si="9"/>
+        <v>16.543014996053671</v>
+      </c>
+      <c r="N53">
         <f t="shared" si="7"/>
-        <v>16.253968253968253</v>
-      </c>
-      <c r="N53">
-        <f t="shared" si="5"/>
-        <v>21.231746031746031</v>
+        <v>22.333070244672456</v>
       </c>
       <c r="O53">
-        <f t="shared" si="5"/>
-        <v>24.076190476190476</v>
+        <f t="shared" si="7"/>
+        <v>24.5043409629045</v>
       </c>
       <c r="P53">
-        <f t="shared" si="5"/>
-        <v>5.9936507936507937</v>
+        <f t="shared" si="7"/>
+        <v>6.1002367797947912</v>
       </c>
     </row>
     <row r="54" spans="1:16" x14ac:dyDescent="0.25">
@@ -3744,7 +4051,7 @@
         <v>16</v>
       </c>
       <c r="E54">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="F54">
         <v>4</v>
@@ -3753,34 +4060,34 @@
         <v>2</v>
       </c>
       <c r="H54">
-        <v>110</v>
+        <v>114</v>
       </c>
       <c r="J54" t="s">
         <v>9</v>
       </c>
       <c r="K54">
+        <f t="shared" si="10"/>
+        <v>31.49171270718232</v>
+      </c>
+      <c r="L54">
         <f t="shared" si="8"/>
-        <v>30.555555555555557</v>
-      </c>
-      <c r="L54">
-        <f t="shared" si="6"/>
-        <v>21.388888888888889</v>
+        <v>22.044198895027623</v>
       </c>
       <c r="M54">
+        <f t="shared" si="9"/>
+        <v>14.396211523283347</v>
+      </c>
+      <c r="N54">
         <f t="shared" si="7"/>
-        <v>13.968253968253968</v>
-      </c>
-      <c r="N54">
-        <f t="shared" si="5"/>
-        <v>18.246031746031747</v>
+        <v>19.434885556432519</v>
       </c>
       <c r="O54">
-        <f t="shared" si="5"/>
-        <v>20.69047619047619</v>
+        <f t="shared" si="7"/>
+        <v>21.324388318863456</v>
       </c>
       <c r="P54">
-        <f t="shared" si="5"/>
-        <v>5.1507936507936511</v>
+        <f t="shared" si="7"/>
+        <v>5.3086029992107342</v>
       </c>
     </row>
     <row r="55" spans="1:16" x14ac:dyDescent="0.25">
@@ -3812,28 +4119,28 @@
         <v>25</v>
       </c>
       <c r="K55">
+        <f t="shared" si="10"/>
+        <v>49.171270718232044</v>
+      </c>
+      <c r="L55">
         <f t="shared" si="8"/>
-        <v>49.444444444444443</v>
-      </c>
-      <c r="L55">
-        <f t="shared" si="6"/>
-        <v>34.611111111111114</v>
+        <v>34.41988950276243</v>
       </c>
       <c r="M55">
+        <f t="shared" si="9"/>
+        <v>22.478295185477506</v>
+      </c>
+      <c r="N55">
         <f t="shared" si="7"/>
-        <v>22.603174603174605</v>
-      </c>
-      <c r="N55">
-        <f t="shared" si="5"/>
-        <v>29.525396825396825</v>
+        <v>30.345698500394633</v>
       </c>
       <c r="O55">
-        <f t="shared" si="5"/>
-        <v>33.480952380952381</v>
+        <f t="shared" si="7"/>
+        <v>33.295974743488557</v>
       </c>
       <c r="P55">
-        <f t="shared" si="5"/>
-        <v>8.3349206349206355</v>
+        <f t="shared" si="7"/>
+        <v>8.2888713496448307</v>
       </c>
     </row>
     <row r="56" spans="1:16" x14ac:dyDescent="0.25">
@@ -3850,7 +4157,7 @@
         <v>160</v>
       </c>
       <c r="E56">
-        <v>209</v>
+        <v>216</v>
       </c>
       <c r="F56">
         <v>237</v>
@@ -3859,7 +4166,7 @@
         <v>59</v>
       </c>
       <c r="H56">
-        <v>1260</v>
+        <v>1267</v>
       </c>
     </row>
     <row r="59" spans="1:16" x14ac:dyDescent="0.25">
@@ -3911,55 +4218,55 @@
         <v>4</v>
       </c>
       <c r="B60">
-        <f>((B49-K493)^2)/K49</f>
-        <v>102.63050847457627</v>
+        <f>((B49-K49)^2)/K49</f>
+        <v>19.797363048974617</v>
       </c>
       <c r="C60">
-        <f>((C49-L493)^2)/L49</f>
-        <v>8.5423728813559325</v>
+        <f t="shared" ref="C60:G66" si="11">((C49-L49)^2)/L49</f>
+        <v>3.4075100664856266</v>
       </c>
       <c r="D60">
-        <f>((D49-M493)^2)/M49</f>
-        <v>4.2711864406779663</v>
+        <f t="shared" si="11"/>
+        <v>3.1962570064077691</v>
       </c>
       <c r="E60">
-        <f>((E49-N493)^2)/N49</f>
-        <v>2.503446598005028</v>
+        <f t="shared" si="11"/>
+        <v>8.5525850628563891</v>
       </c>
       <c r="F60">
-        <f>((F49-O493)^2)/O49</f>
-        <v>19.869126796824716</v>
+        <f t="shared" si="11"/>
+        <v>5.2123304987378646E-2</v>
       </c>
       <c r="G60">
-        <f>((G49-P493)^2)/P49</f>
-        <v>18.098247629991381</v>
+        <f t="shared" si="11"/>
+        <v>3.6936632212708664</v>
       </c>
       <c r="J60" t="s">
         <v>4</v>
       </c>
       <c r="K60">
-        <f>(B49-K49)/SQRT(K49)</f>
-        <v>4.4054836570295031</v>
+        <f>(B49-K49)/SQRT(K49*(1-$H49/$H$56)*(1-B$56/$H$56))</f>
+        <v>5.4920642134221636</v>
       </c>
       <c r="L60">
-        <f t="shared" ref="L60:P66" si="9">(C49-L49)/SQRT(L49)</f>
-        <v>-1.8673021517152428</v>
+        <f>(C49-L49)/SQRT(L49*(1-$H49/$H$56)*(1-C$56/$H$56))</f>
+        <v>-2.1582896415477171</v>
       </c>
       <c r="M60">
-        <f t="shared" si="9"/>
-        <v>-1.8042487147854505</v>
+        <f>(D49-M49)/SQRT(M49*(1-$H49/$H$56)*(1-D$56/$H$56))</f>
+        <v>-2.0084620800211743</v>
       </c>
       <c r="N60">
-        <f t="shared" si="9"/>
-        <v>-2.8419117634122455</v>
+        <f>(E49-N49)/SQRT(N49*(1-$H49/$H$56)*(1-E$56/$H$56))</f>
+        <v>-3.3718165941885085</v>
       </c>
       <c r="O60">
-        <f t="shared" si="9"/>
-        <v>-0.25370236905242149</v>
+        <f>(F49-O49)/SQRT(O49*(1-$H49/$H$56)*(1-F$56/$H$56))</f>
+        <v>-0.2658973204616274</v>
       </c>
       <c r="P60">
-        <f t="shared" si="9"/>
-        <v>1.9035872597252292</v>
+        <f>(G49-P49)/SQRT(P49*(1-$H49/$H$56)*(1-G$56/$H$56))</f>
+        <v>2.0668634289343135</v>
       </c>
     </row>
     <row r="61" spans="1:16" x14ac:dyDescent="0.25">
@@ -3967,55 +4274,55 @@
         <v>29</v>
       </c>
       <c r="B61">
-        <f>((B50-K494)^2)/K50</f>
-        <v>136.41833810888252</v>
+        <f>((B50-K50)^2)/K50</f>
+        <v>3.585057544048508</v>
       </c>
       <c r="C61">
-        <f>((C50-L494)^2)/L50</f>
-        <v>76.391322144903796</v>
+        <f t="shared" si="11"/>
+        <v>0.30190622434602771</v>
       </c>
       <c r="D61">
-        <f>((D50-M494)^2)/M50</f>
-        <v>17.690544412607451</v>
+        <f t="shared" si="11"/>
+        <v>5.8614376853022394</v>
       </c>
       <c r="E61">
-        <f>((E50-N494)^2)/N50</f>
-        <v>46.709532361771842</v>
+        <f t="shared" si="11"/>
+        <v>0.94491211573957912</v>
       </c>
       <c r="F61">
-        <f>((F50-O494)^2)/O50</f>
-        <v>64.361104058612312</v>
+        <f t="shared" si="11"/>
+        <v>1.2229696105640455E-3</v>
       </c>
       <c r="G61">
-        <f>((G50-P494)^2)/P50</f>
-        <v>17.684425234325676</v>
+        <f t="shared" si="11"/>
+        <v>3.4447889643972565E-2</v>
       </c>
       <c r="J61" t="s">
         <v>29</v>
       </c>
       <c r="K61">
-        <f>(B50-K50)/SQRT(K50)</f>
-        <v>1.8337891245524842</v>
+        <f>(B50-K50)/SQRT(K50*(1-$H50/$H$56)*(1-B$56/$H$56))</f>
+        <v>2.6146807645880816</v>
       </c>
       <c r="L61">
-        <f t="shared" si="9"/>
-        <v>0.50242736391932075</v>
+        <f t="shared" ref="L61:L66" si="12">(C50-L50)/SQRT(L50*(1-$H50/$H$56)*(1-C$56/$H$56))</f>
+        <v>0.71873014400110835</v>
       </c>
       <c r="M61">
-        <f>(D50-M50)/SQRT(M50)</f>
-        <v>-2.451123156854377</v>
+        <f t="shared" ref="M61:M66" si="13">(D50-M50)/SQRT(M50*(1-$H50/$H$56)*(1-D$56/$H$56))</f>
+        <v>-3.0428709913576326</v>
       </c>
       <c r="N61">
-        <f t="shared" si="9"/>
-        <v>-0.77408972442113111</v>
+        <f t="shared" ref="N61:N66" si="14">(E50-N50)/SQRT(N50*(1-$H50/$H$56)*(1-E$56/$H$56))</f>
+        <v>-1.2538616661581017</v>
       </c>
       <c r="O61">
-        <f t="shared" si="9"/>
-        <v>-7.9637640914365052E-2</v>
+        <f t="shared" ref="O61:O66" si="15">(F50-O50)/SQRT(O50*(1-$H50/$H$56)*(1-F$56/$H$56))</f>
+        <v>-4.5566376539646403E-2</v>
       </c>
       <c r="P61">
-        <f t="shared" si="9"/>
-        <v>0.16275357565709073</v>
+        <f t="shared" ref="P61:P66" si="16">(G50-P50)/SQRT(P50*(1-$H50/$H$56)*(1-G$56/$H$56))</f>
+        <v>0.22330740138774252</v>
       </c>
     </row>
     <row r="62" spans="1:16" x14ac:dyDescent="0.25">
@@ -4023,55 +4330,55 @@
         <v>6</v>
       </c>
       <c r="B62">
-        <f>((B51-K495)^2)/K51</f>
-        <v>16.472268907563024</v>
+        <f t="shared" ref="B62:B66" si="17">((B51-K51)^2)/K51</f>
+        <v>16.309637866196205</v>
       </c>
       <c r="C62">
-        <f>((C51-L495)^2)/L51</f>
-        <v>47.733493397358941</v>
+        <f t="shared" si="11"/>
+        <v>2.0778919302527739E-2</v>
       </c>
       <c r="D62">
-        <f>((D51-M495)^2)/M51</f>
-        <v>67.003676470588232</v>
+        <f t="shared" si="11"/>
+        <v>7.4311677364315871</v>
       </c>
       <c r="E62">
-        <f>((E51-N495)^2)/N51</f>
-        <v>46.836476217281174</v>
+        <f t="shared" si="11"/>
+        <v>0.14498323884495509</v>
       </c>
       <c r="F62">
-        <f>((F51-O495)^2)/O51</f>
-        <v>88.659717051377513</v>
+        <f t="shared" si="11"/>
+        <v>7.6716080515708596</v>
       </c>
       <c r="G62">
-        <f>((G51-P495)^2)/P51</f>
-        <v>4.3968095712861421</v>
+        <f t="shared" si="11"/>
+        <v>1.504109219303416</v>
       </c>
       <c r="J62" t="s">
         <v>6</v>
       </c>
       <c r="K62">
-        <f t="shared" ref="K61:K66" si="10">(B51-K51)/SQRT(K51)</f>
-        <v>-4.072269639730913</v>
+        <f>(B51-K51)/SQRT(K51*(1-$H51/$H$56)*(1-B$56/$H$56))</f>
+        <v>-5.2675227355524452</v>
       </c>
       <c r="L62">
-        <f t="shared" si="9"/>
-        <v>0.10616579080250535</v>
+        <f t="shared" si="12"/>
+        <v>0.1780963249567569</v>
       </c>
       <c r="M62">
-        <f t="shared" si="9"/>
-        <v>2.688103177486024</v>
+        <f t="shared" si="13"/>
+        <v>3.2361127849020757</v>
       </c>
       <c r="N62">
-        <f t="shared" si="9"/>
-        <v>0.56058362004160378</v>
+        <f t="shared" si="14"/>
+        <v>0.46390223854658152</v>
       </c>
       <c r="O62">
-        <f t="shared" si="9"/>
-        <v>2.7251392107641363</v>
+        <f t="shared" si="15"/>
+        <v>3.4087371854024338</v>
       </c>
       <c r="P62">
-        <f t="shared" si="9"/>
-        <v>-1.2414725191201719</v>
+        <f t="shared" si="16"/>
+        <v>-1.3937187636038388</v>
       </c>
     </row>
     <row r="63" spans="1:16" x14ac:dyDescent="0.25">
@@ -4079,55 +4386,55 @@
         <v>27</v>
       </c>
       <c r="B63">
-        <f>((B52-K496)^2)/K52</f>
-        <v>33.565467625899281</v>
+        <f t="shared" si="17"/>
+        <v>0.14973250129178445</v>
       </c>
       <c r="C63">
-        <f>((C52-L496)^2)/L52</f>
-        <v>47.95066803699897</v>
+        <f t="shared" si="11"/>
+        <v>3.0955136758785566</v>
       </c>
       <c r="D63">
-        <f>((D52-M496)^2)/M52</f>
-        <v>38.298561151079134</v>
+        <f t="shared" si="11"/>
+        <v>4.0646063890797386</v>
       </c>
       <c r="E63">
-        <f>((E52-N496)^2)/N52</f>
-        <v>3.5131320780696016</v>
+        <f t="shared" si="11"/>
+        <v>9.1150873302936173</v>
       </c>
       <c r="F63">
-        <f>((F52-O496)^2)/O52</f>
-        <v>22.030780438939988</v>
+        <f t="shared" si="11"/>
+        <v>0.1539629295834011</v>
       </c>
       <c r="G63">
-        <f>((G52-P496)^2)/P52</f>
-        <v>9.8329472015607848</v>
+        <f t="shared" si="11"/>
+        <v>0.36034500961295357</v>
       </c>
       <c r="J63" t="s">
         <v>27</v>
       </c>
       <c r="K63">
-        <f t="shared" si="10"/>
-        <v>-0.42021272828222622</v>
+        <f>(B52-K52)/SQRT(K52*(1-$H52/$H$56)*(1-B$56/$H$56))</f>
+        <v>-0.48205371817383663</v>
       </c>
       <c r="L63">
-        <f t="shared" si="9"/>
-        <v>1.7258174337909411</v>
+        <f t="shared" si="12"/>
+        <v>2.0761703315433313</v>
       </c>
       <c r="M63">
-        <f t="shared" si="9"/>
-        <v>1.9872983676018019</v>
+        <f t="shared" si="13"/>
+        <v>2.2859014460205067</v>
       </c>
       <c r="N63">
-        <f t="shared" si="9"/>
-        <v>-2.9273676373866691</v>
+        <f t="shared" si="14"/>
+        <v>-3.5131858429096736</v>
       </c>
       <c r="O63">
-        <f t="shared" si="9"/>
-        <v>-0.41954562824332053</v>
+        <f t="shared" si="15"/>
+        <v>-0.46122361542787699</v>
       </c>
       <c r="P63">
-        <f t="shared" si="9"/>
-        <v>0.5845317444681204</v>
+        <f t="shared" si="16"/>
+        <v>0.65155015716761744</v>
       </c>
     </row>
     <row r="64" spans="1:16" x14ac:dyDescent="0.25">
@@ -4135,55 +4442,55 @@
         <v>37</v>
       </c>
       <c r="B64">
-        <f>((B53-K497)^2)/K53</f>
-        <v>64.8</v>
+        <f t="shared" si="17"/>
+        <v>3.8556315634093865</v>
       </c>
       <c r="C64">
-        <f>((C53-L497)^2)/L53</f>
-        <v>17.71875</v>
+        <f t="shared" si="11"/>
+        <v>0.74065201805069425</v>
       </c>
       <c r="D64">
-        <f>((D53-M497)^2)/M53</f>
-        <v>24.609375</v>
+        <f t="shared" si="11"/>
+        <v>0.72240430903076891</v>
       </c>
       <c r="E64">
-        <f>((E53-N497)^2)/N53</f>
-        <v>0.18839712918660287</v>
+        <f t="shared" si="11"/>
+        <v>13.452486416569542</v>
       </c>
       <c r="F64">
-        <f>((F53-O497)^2)/O53</f>
-        <v>32.563291139240505</v>
+        <f t="shared" si="11"/>
+        <v>0.4986721382193437</v>
       </c>
       <c r="G64">
-        <f>((G53-P497)^2)/P53</f>
-        <v>13.514300847457626</v>
+        <f t="shared" si="11"/>
+        <v>1.3784098940398415</v>
       </c>
       <c r="J64" t="s">
         <v>37</v>
       </c>
       <c r="K64">
-        <f t="shared" si="10"/>
-        <v>2.0869967789998034</v>
+        <f t="shared" ref="K61:K66" si="18">(B53-K53)/SQRT(K53*(1-$H53/$H$56)*(1-B$56/$H$56))</f>
+        <v>2.4375332289575526</v>
       </c>
       <c r="L64">
-        <f t="shared" si="9"/>
-        <v>-0.77951195557790465</v>
+        <f t="shared" si="12"/>
+        <v>-1.0119734219963863</v>
       </c>
       <c r="M64">
-        <f t="shared" si="9"/>
-        <v>0.92916266281435045</v>
+        <f t="shared" si="13"/>
+        <v>0.96029308745601505</v>
       </c>
       <c r="N64">
-        <f t="shared" si="9"/>
-        <v>-4.1737445011563219</v>
+        <f t="shared" si="14"/>
+        <v>-4.2529215553917368</v>
       </c>
       <c r="O64">
-        <f t="shared" si="9"/>
-        <v>0.79967594401168685</v>
+        <f t="shared" si="15"/>
+        <v>0.8271349820637478</v>
       </c>
       <c r="P64">
-        <f t="shared" si="9"/>
-        <v>1.2279868244848642</v>
+        <f t="shared" si="16"/>
+        <v>1.2698229527821767</v>
       </c>
     </row>
     <row r="65" spans="1:16" x14ac:dyDescent="0.25">
@@ -4191,120 +4498,146 @@
         <v>9</v>
       </c>
       <c r="B65">
-        <f>((B54-K498)^2)/K54</f>
-        <v>3.2727272727272725</v>
+        <f t="shared" si="17"/>
+        <v>14.667151303673547</v>
       </c>
       <c r="C65">
-        <f>((C54-L498)^2)/L54</f>
-        <v>34.08311688311688</v>
+        <f t="shared" si="11"/>
+        <v>1.1141237070576999</v>
       </c>
       <c r="D65">
-        <f>((D54-M498)^2)/M54</f>
-        <v>18.327272727272728</v>
+        <f t="shared" si="11"/>
+        <v>0.17866766363422368</v>
       </c>
       <c r="E65">
-        <f>((E54-N498)^2)/N54</f>
-        <v>142.55154414963027</v>
+        <f t="shared" si="11"/>
+        <v>65.082830650649527</v>
       </c>
       <c r="F65">
-        <f>((F54-O498)^2)/O54</f>
-        <v>0.7733026467203683</v>
+        <f t="shared" si="11"/>
+        <v>14.074702923941551</v>
       </c>
       <c r="G65">
-        <f>((G54-P498)^2)/P54</f>
-        <v>0.77657935285053925</v>
+        <f t="shared" si="11"/>
+        <v>2.0620969034628898</v>
       </c>
       <c r="J65" t="s">
         <v>9</v>
       </c>
       <c r="K65">
-        <f t="shared" si="10"/>
-        <v>-3.7186399164590846</v>
+        <f>(B54-K54)/SQRT(K54*(1-$H54/$H$56)*(1-B$56/$H$56))</f>
+        <v>-4.7190021961399848</v>
       </c>
       <c r="L65">
-        <f t="shared" si="9"/>
-        <v>1.2132624497633526</v>
+        <f t="shared" si="12"/>
+        <v>1.2319787619535989</v>
       </c>
       <c r="M65">
-        <f t="shared" si="9"/>
-        <v>0.54362367086680052</v>
+        <f t="shared" si="13"/>
+        <v>0.47403578732849494</v>
       </c>
       <c r="N65">
-        <f t="shared" si="9"/>
-        <v>7.6679577395589504</v>
+        <f t="shared" si="14"/>
+        <v>9.2852546735458805</v>
       </c>
       <c r="O65">
-        <f t="shared" si="9"/>
-        <v>-3.669302227562695</v>
+        <f t="shared" si="15"/>
+        <v>-4.3617720712734034</v>
       </c>
       <c r="P65">
-        <f t="shared" si="9"/>
-        <v>-1.388298600317738</v>
+        <f t="shared" si="16"/>
+        <v>-1.5416402093239689</v>
       </c>
     </row>
     <row r="66" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="H66" t="s">
-        <v>70</v>
+      <c r="B66">
+        <f t="shared" si="17"/>
+        <v>1.396734744552734E-2</v>
+      </c>
+      <c r="C66">
+        <f t="shared" si="11"/>
+        <v>1.1974175926500712</v>
+      </c>
+      <c r="D66">
+        <f t="shared" si="11"/>
+        <v>1.3351420955898656</v>
+      </c>
+      <c r="E66">
+        <f t="shared" si="11"/>
+        <v>7.0767378262373297</v>
+      </c>
+      <c r="F66">
+        <f t="shared" si="11"/>
+        <v>5.0443050509842435E-2</v>
+      </c>
+      <c r="G66">
+        <f t="shared" si="11"/>
+        <v>0.63204407864882972</v>
       </c>
       <c r="J66" t="s">
         <v>25</v>
       </c>
       <c r="K66">
-        <f t="shared" si="10"/>
-        <v>7.9007577189996431E-2</v>
+        <f>(B55-K55)/SQRT(K55*(1-$H55/$H$56)*(1-B$56/$H$56))</f>
+        <v>0.14984248799038094</v>
       </c>
       <c r="L66">
-        <f t="shared" si="9"/>
-        <v>-1.1237421876789797</v>
+        <f t="shared" si="12"/>
+        <v>-1.3141957076713142</v>
       </c>
       <c r="M66">
-        <f t="shared" si="9"/>
-        <v>-1.1785538638162352</v>
+        <f t="shared" si="13"/>
+        <v>-1.3333759239663781</v>
       </c>
       <c r="N66">
-        <f t="shared" si="9"/>
-        <v>2.8478797615112343</v>
+        <f t="shared" si="14"/>
+        <v>3.1504882936300946</v>
       </c>
       <c r="O66">
-        <f t="shared" si="9"/>
-        <v>-0.25594237326420488</v>
+        <f t="shared" si="15"/>
+        <v>-0.26868581187039664</v>
       </c>
       <c r="P66">
-        <f t="shared" si="9"/>
-        <v>-0.80876321286432373</v>
+        <f t="shared" si="16"/>
+        <v>-0.87821912668142776</v>
       </c>
     </row>
     <row r="67" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
         <v>15</v>
       </c>
-      <c r="B67">
-        <f>SUM(B60:B65)</f>
-        <v>357.15931038964834</v>
-      </c>
-      <c r="C67">
-        <f t="shared" ref="C67:G67" si="11">SUM(C60:C65)</f>
-        <v>232.41972334373449</v>
-      </c>
-      <c r="D67">
-        <f t="shared" si="11"/>
-        <v>170.20061620222549</v>
-      </c>
-      <c r="E67">
-        <f t="shared" si="11"/>
-        <v>242.3025285339445</v>
-      </c>
-      <c r="F67">
-        <f t="shared" si="11"/>
-        <v>228.2573221317154</v>
-      </c>
-      <c r="G67">
-        <f t="shared" si="11"/>
-        <v>64.303309837472142</v>
-      </c>
-      <c r="H67">
-        <f>SUM(B67:G67)</f>
-        <v>1294.6428104387405</v>
+      <c r="H67" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="68" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="B68">
+        <f>SUM(B60:B66)</f>
+        <v>58.37854117503958</v>
+      </c>
+      <c r="C68">
+        <f t="shared" ref="C68:F68" si="19">SUM(C60:C66)</f>
+        <v>9.877902203771205</v>
+      </c>
+      <c r="D68">
+        <f t="shared" si="19"/>
+        <v>22.789682885476189</v>
+      </c>
+      <c r="E68">
+        <f t="shared" si="19"/>
+        <v>104.36962264119094</v>
+      </c>
+      <c r="F68">
+        <f t="shared" si="19"/>
+        <v>22.50273536842294</v>
+      </c>
+      <c r="G68">
+        <f>SUM(G60:G66)</f>
+        <v>9.6651162159827688</v>
+      </c>
+      <c r="H68">
+        <f>SUM(B68:G68)</f>
+        <v>227.58360048988365</v>
       </c>
     </row>
     <row r="71" spans="1:16" x14ac:dyDescent="0.25">
@@ -4312,21 +4645,24 @@
         <v>72</v>
       </c>
       <c r="B71" t="s">
+        <v>80</v>
+      </c>
+      <c r="C71" t="s">
         <v>0</v>
       </c>
-      <c r="C71" t="s">
+      <c r="D71" t="s">
         <v>2</v>
       </c>
-      <c r="D71" t="s">
+      <c r="E71" t="s">
         <v>63</v>
       </c>
-      <c r="E71" t="s">
+      <c r="F71" t="s">
         <v>64</v>
       </c>
-      <c r="F71" t="s">
+      <c r="G71" t="s">
         <v>65</v>
       </c>
-      <c r="G71" t="s">
+      <c r="H71" t="s">
         <v>66</v>
       </c>
     </row>
@@ -4334,161 +4670,182 @@
       <c r="A72" t="s">
         <v>4</v>
       </c>
-      <c r="B72" s="6">
-        <v>4.4054836570295031</v>
+      <c r="B72" t="s">
+        <v>4</v>
       </c>
       <c r="C72" s="6">
-        <v>-1.8673021517152428</v>
+        <v>5.4920642134221636</v>
       </c>
       <c r="D72" s="6">
-        <v>-1.8042487147854505</v>
+        <v>-2.1582896415477171</v>
       </c>
       <c r="E72" s="6">
-        <v>-2.8419117634122455</v>
+        <v>-2.0084620800211743</v>
       </c>
       <c r="F72" s="6">
-        <v>-0.25370236905242149</v>
+        <v>-3.3718165941885085</v>
       </c>
       <c r="G72" s="6">
-        <v>1.9035872597252292</v>
+        <v>-0.2658973204616274</v>
+      </c>
+      <c r="H72" s="6">
+        <v>2.0668634289343135</v>
       </c>
     </row>
     <row r="73" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
         <v>29</v>
       </c>
-      <c r="B73" s="6">
-        <v>1.8337891245524842</v>
+      <c r="B73" t="s">
+        <v>29</v>
       </c>
       <c r="C73" s="6">
-        <v>0.50242736391932075</v>
+        <v>2.6146807645880816</v>
       </c>
       <c r="D73" s="6">
-        <v>-2.451123156854377</v>
+        <v>0.71873014400110835</v>
       </c>
       <c r="E73" s="6">
-        <v>-0.77408972442113111</v>
+        <v>-3.0428709913576326</v>
       </c>
       <c r="F73" s="6">
-        <v>-7.9637640914365052E-2</v>
+        <v>-1.2538616661581017</v>
       </c>
       <c r="G73" s="6">
-        <v>0.16275357565709073</v>
+        <v>-4.5566376539646403E-2</v>
+      </c>
+      <c r="H73" s="6">
+        <v>0.22330740138774252</v>
       </c>
     </row>
     <row r="74" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
         <v>6</v>
       </c>
-      <c r="B74" s="6">
-        <v>-4.072269639730913</v>
+      <c r="B74" t="s">
+        <v>6</v>
       </c>
       <c r="C74" s="6">
-        <v>0.10616579080250535</v>
+        <v>-5.2675227355524452</v>
       </c>
       <c r="D74" s="6">
-        <v>2.688103177486024</v>
+        <v>0.1780963249567569</v>
       </c>
       <c r="E74" s="6">
-        <v>0.56058362004160378</v>
+        <v>3.2361127849020757</v>
       </c>
       <c r="F74" s="6">
-        <v>2.7251392107641363</v>
+        <v>0.46390223854658152</v>
       </c>
       <c r="G74" s="6">
-        <v>-1.2414725191201719</v>
+        <v>3.4087371854024338</v>
+      </c>
+      <c r="H74" s="6">
+        <v>-1.3937187636038388</v>
       </c>
     </row>
     <row r="75" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
         <v>27</v>
       </c>
-      <c r="B75" s="6">
-        <v>-0.42021272828222622</v>
+      <c r="B75" t="s">
+        <v>27</v>
       </c>
       <c r="C75" s="6">
-        <v>1.7258174337909411</v>
+        <v>-0.48205371817383663</v>
       </c>
       <c r="D75" s="6">
-        <v>1.9872983676018019</v>
+        <v>2.0761703315433313</v>
       </c>
       <c r="E75" s="6">
-        <v>-2.9273676373866691</v>
+        <v>2.2859014460205067</v>
       </c>
       <c r="F75" s="6">
-        <v>-0.41954562824332053</v>
+        <v>-3.5131858429096736</v>
       </c>
       <c r="G75" s="6">
-        <v>0.5845317444681204</v>
+        <v>-0.46122361542787699</v>
+      </c>
+      <c r="H75" s="6">
+        <v>0.65155015716761744</v>
       </c>
     </row>
     <row r="76" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
         <v>37</v>
       </c>
-      <c r="B76" s="6">
-        <v>2.0869967789998034</v>
+      <c r="B76" t="s">
+        <v>37</v>
       </c>
       <c r="C76" s="6">
-        <v>-0.77951195557790465</v>
+        <v>2.4375332289575526</v>
       </c>
       <c r="D76" s="6">
-        <v>0.92916266281435045</v>
+        <v>-1.0119734219963863</v>
       </c>
       <c r="E76" s="6">
-        <v>-4.1737445011563219</v>
+        <v>0.96029308745601505</v>
       </c>
       <c r="F76" s="6">
-        <v>0.79967594401168685</v>
+        <v>-4.2529215553917368</v>
       </c>
       <c r="G76" s="6">
-        <v>1.2279868244848642</v>
+        <v>0.8271349820637478</v>
+      </c>
+      <c r="H76" s="6">
+        <v>1.2698229527821767</v>
       </c>
     </row>
     <row r="77" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
         <v>9</v>
       </c>
-      <c r="B77" s="6">
-        <v>-3.7186399164590846</v>
+      <c r="B77" t="s">
+        <v>9</v>
       </c>
       <c r="C77" s="6">
-        <v>1.2132624497633526</v>
+        <v>-4.7190021961399848</v>
       </c>
       <c r="D77" s="6">
-        <v>0.54362367086680052</v>
+        <v>1.2319787619535989</v>
       </c>
       <c r="E77" s="6">
-        <v>7.6679577395589504</v>
+        <v>0.47403578732849494</v>
       </c>
       <c r="F77" s="6">
-        <v>-3.669302227562695</v>
+        <v>9.2852546735458805</v>
       </c>
       <c r="G77" s="6">
-        <v>-1.388298600317738</v>
+        <v>-4.3617720712734034</v>
+      </c>
+      <c r="H77" s="6">
+        <v>-1.5416402093239689</v>
       </c>
     </row>
     <row r="78" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
         <v>25</v>
       </c>
-      <c r="B78" s="6">
-        <v>7.9007577189996431E-2</v>
+      <c r="B78" t="s">
+        <v>25</v>
       </c>
       <c r="C78" s="6">
-        <v>-1.1237421876789797</v>
+        <v>0.14984248799038094</v>
       </c>
       <c r="D78" s="6">
-        <v>-1.1785538638162352</v>
+        <v>-1.3141957076713142</v>
       </c>
       <c r="E78" s="6">
-        <v>2.8478797615112343</v>
+        <v>-1.3333759239663781</v>
       </c>
       <c r="F78" s="6">
-        <v>-0.25594237326420488</v>
+        <v>3.1504882936300946</v>
       </c>
       <c r="G78" s="6">
-        <v>-0.80876321286432373</v>
+        <v>-0.26868581187039664</v>
+      </c>
+      <c r="H78" s="6">
+        <v>-0.87821912668142776</v>
       </c>
     </row>
     <row r="83" spans="1:16" x14ac:dyDescent="0.25">
@@ -4569,23 +4926,23 @@
         <v>7.5787965616045847</v>
       </c>
       <c r="L84">
-        <f t="shared" ref="L84:P88" si="12">$H84*C$89/$H$89</f>
+        <f t="shared" ref="L84:P88" si="20">$H84*C$89/$H$89</f>
         <v>4.7449856733524358</v>
       </c>
       <c r="M84">
-        <f t="shared" si="12"/>
+        <f t="shared" si="20"/>
         <v>1.845272206303725</v>
       </c>
       <c r="N84">
-        <f t="shared" si="12"/>
+        <f t="shared" si="20"/>
         <v>3.4269340974212033</v>
       </c>
       <c r="O84">
-        <f t="shared" si="12"/>
+        <f t="shared" si="20"/>
         <v>4.2836676217765044</v>
       </c>
       <c r="P84">
-        <f t="shared" si="12"/>
+        <f t="shared" si="20"/>
         <v>1.1203438395415473</v>
       </c>
     </row>
@@ -4612,34 +4969,34 @@
         <v>7</v>
       </c>
       <c r="H85">
-        <f t="shared" ref="H85:H88" si="13">SUM(B85:G85)</f>
+        <f t="shared" ref="H85:H88" si="21">SUM(B85:G85)</f>
         <v>112</v>
       </c>
       <c r="J85" t="s">
         <v>49</v>
       </c>
       <c r="K85">
-        <f t="shared" ref="K85:K88" si="14">$H85*B$89/$H$89</f>
+        <f t="shared" ref="K85:K88" si="22">$H85*B$89/$H$89</f>
         <v>36.905444126074499</v>
       </c>
       <c r="L85">
-        <f t="shared" si="12"/>
+        <f t="shared" si="20"/>
         <v>23.106017191977077</v>
       </c>
       <c r="M85">
-        <f t="shared" si="12"/>
+        <f t="shared" si="20"/>
         <v>8.9856733524355299</v>
       </c>
       <c r="N85">
-        <f t="shared" si="12"/>
+        <f t="shared" si="20"/>
         <v>16.687679083094554</v>
       </c>
       <c r="O85">
-        <f t="shared" si="12"/>
+        <f t="shared" si="20"/>
         <v>20.859598853868196</v>
       </c>
       <c r="P85">
-        <f t="shared" si="12"/>
+        <f t="shared" si="20"/>
         <v>5.455587392550143</v>
       </c>
     </row>
@@ -4666,34 +5023,34 @@
         <v>9</v>
       </c>
       <c r="H86">
-        <f t="shared" si="13"/>
+        <f t="shared" si="21"/>
         <v>143</v>
       </c>
       <c r="J86" t="s">
         <v>50</v>
       </c>
       <c r="K86">
-        <f t="shared" si="14"/>
+        <f t="shared" si="22"/>
         <v>47.120343839541547</v>
       </c>
       <c r="L86">
-        <f t="shared" si="12"/>
+        <f t="shared" si="20"/>
         <v>29.501432664756447</v>
       </c>
       <c r="M86">
-        <f t="shared" si="12"/>
+        <f t="shared" si="20"/>
         <v>11.472779369627506</v>
       </c>
       <c r="N86">
-        <f t="shared" si="12"/>
+        <f t="shared" si="20"/>
         <v>21.306590257879655</v>
       </c>
       <c r="O86">
-        <f t="shared" si="12"/>
+        <f t="shared" si="20"/>
         <v>26.633237822349571</v>
       </c>
       <c r="P86">
-        <f t="shared" si="12"/>
+        <f t="shared" si="20"/>
         <v>6.9656160458452723</v>
       </c>
     </row>
@@ -4720,34 +5077,34 @@
         <v>0</v>
       </c>
       <c r="H87">
-        <f t="shared" si="13"/>
+        <f t="shared" si="21"/>
         <v>36</v>
       </c>
       <c r="J87" t="s">
         <v>51</v>
       </c>
       <c r="K87">
-        <f t="shared" si="14"/>
+        <f t="shared" si="22"/>
         <v>11.862464183381089</v>
       </c>
       <c r="L87">
-        <f t="shared" si="12"/>
+        <f t="shared" si="20"/>
         <v>7.4269340974212037</v>
       </c>
       <c r="M87">
-        <f t="shared" si="12"/>
+        <f t="shared" si="20"/>
         <v>2.8882521489971347</v>
       </c>
       <c r="N87">
-        <f t="shared" si="12"/>
+        <f t="shared" si="20"/>
         <v>5.3638968481375358</v>
       </c>
       <c r="O87">
-        <f t="shared" si="12"/>
+        <f t="shared" si="20"/>
         <v>6.7048710601719197</v>
       </c>
       <c r="P87">
-        <f t="shared" si="12"/>
+        <f t="shared" si="20"/>
         <v>1.7535816618911175</v>
       </c>
     </row>
@@ -4774,34 +5131,34 @@
         <v>1</v>
       </c>
       <c r="H88">
-        <f t="shared" si="13"/>
+        <f t="shared" si="21"/>
         <v>35</v>
       </c>
       <c r="J88" t="s">
         <v>52</v>
       </c>
       <c r="K88">
-        <f t="shared" si="14"/>
+        <f t="shared" si="22"/>
         <v>11.53295128939828</v>
       </c>
       <c r="L88">
-        <f t="shared" si="12"/>
+        <f t="shared" si="20"/>
         <v>7.2206303724928365</v>
       </c>
       <c r="M88">
-        <f t="shared" si="12"/>
+        <f t="shared" si="20"/>
         <v>2.8080229226361033</v>
       </c>
       <c r="N88">
-        <f t="shared" si="12"/>
+        <f t="shared" si="20"/>
         <v>5.2148997134670489</v>
       </c>
       <c r="O88">
-        <f t="shared" si="12"/>
+        <f t="shared" si="20"/>
         <v>6.518624641833811</v>
       </c>
       <c r="P88">
-        <f t="shared" si="12"/>
+        <f t="shared" si="20"/>
         <v>1.7048710601719197</v>
       </c>
     </row>
@@ -4814,23 +5171,23 @@
         <v>115</v>
       </c>
       <c r="C89">
-        <f t="shared" ref="C89:G89" si="15">SUM(C84:C88)</f>
+        <f t="shared" ref="C89:G89" si="23">SUM(C84:C88)</f>
         <v>72</v>
       </c>
       <c r="D89">
-        <f t="shared" si="15"/>
+        <f t="shared" si="23"/>
         <v>28</v>
       </c>
       <c r="E89">
-        <f t="shared" si="15"/>
+        <f t="shared" si="23"/>
         <v>52</v>
       </c>
       <c r="F89">
-        <f t="shared" si="15"/>
+        <f t="shared" si="23"/>
         <v>65</v>
       </c>
       <c r="G89">
-        <f t="shared" si="15"/>
+        <f t="shared" si="23"/>
         <v>17</v>
       </c>
       <c r="H89">
@@ -4887,55 +5244,55 @@
         <v>48</v>
       </c>
       <c r="B93">
-        <f>((B84-K84)^2)/K84</f>
+        <f t="shared" ref="B93:G97" si="24">((B84-K84)^2)/K84</f>
         <v>3.8778513820204634</v>
       </c>
       <c r="C93">
-        <f>((C84-L84)^2)/L84</f>
+        <f t="shared" si="24"/>
         <v>3.8156378472654784</v>
       </c>
       <c r="D93">
-        <f t="shared" ref="D93:G97" si="16">((D84-M84)^2)/M84</f>
+        <f t="shared" si="24"/>
         <v>1.845272206303725</v>
       </c>
       <c r="E93">
-        <f t="shared" si="16"/>
+        <f t="shared" si="24"/>
         <v>3.4269340974212033</v>
       </c>
       <c r="F93">
-        <f t="shared" si="16"/>
+        <f t="shared" si="24"/>
         <v>2.5171124378300163</v>
       </c>
       <c r="G93">
-        <f t="shared" si="16"/>
+        <f t="shared" si="24"/>
         <v>1.1203438395415473</v>
       </c>
       <c r="J93" t="s">
         <v>48</v>
       </c>
       <c r="K93">
-        <f>(B84-K84)/SQRT(K84)</f>
-        <v>1.9692260870759517</v>
+        <f>(B84-K84)/SQRT(K84*(1-$H84/$H$89)*(1-B$89/$H$89))</f>
+        <v>2.4883088180994499</v>
       </c>
       <c r="L93">
-        <f t="shared" ref="L93:P97" si="17">(C84-L84)/SQRT(L84)</f>
-        <v>1.9533657740590928</v>
+        <f t="shared" ref="L93:P97" si="25">(C84-L84)/SQRT(L84*(1-$H84/$H$89)*(1-C$89/$H$89))</f>
+        <v>2.2686124772108611</v>
       </c>
       <c r="M93">
-        <f t="shared" si="17"/>
-        <v>-1.3584079675501484</v>
+        <f t="shared" si="25"/>
+        <v>-1.4655287105051573</v>
       </c>
       <c r="N93">
-        <f t="shared" si="17"/>
-        <v>-1.8511980168045783</v>
+        <f t="shared" si="25"/>
+        <v>-2.0763056158551207</v>
       </c>
       <c r="O93">
-        <f t="shared" si="17"/>
-        <v>-1.5865410293560063</v>
+        <f t="shared" si="25"/>
+        <v>-1.8197375833118294</v>
       </c>
       <c r="P93">
-        <f t="shared" si="17"/>
-        <v>-1.0584629608737128</v>
+        <f t="shared" si="25"/>
+        <v>-1.122853896195074</v>
       </c>
     </row>
     <row r="94" spans="1:16" x14ac:dyDescent="0.25">
@@ -4943,55 +5300,55 @@
         <v>49</v>
       </c>
       <c r="B94">
-        <f t="shared" ref="B94:B97" si="18">((B85-K85)^2)/K85</f>
+        <f t="shared" si="24"/>
         <v>1.3638292192421999</v>
       </c>
       <c r="C94">
-        <f t="shared" ref="C94:C97" si="19">((C85-L85)^2)/L85</f>
+        <f t="shared" si="24"/>
         <v>0.15524834277072816</v>
       </c>
       <c r="D94">
-        <f t="shared" si="16"/>
+        <f t="shared" si="24"/>
         <v>1.7678799850885911</v>
       </c>
       <c r="E94">
-        <f t="shared" si="16"/>
+        <f t="shared" si="24"/>
         <v>1.3167999622154343</v>
       </c>
       <c r="F94">
-        <f t="shared" si="16"/>
+        <f t="shared" si="24"/>
         <v>0.16578017254951369</v>
       </c>
       <c r="G94">
-        <f t="shared" si="16"/>
+        <f t="shared" si="24"/>
         <v>0.43720503960896695</v>
       </c>
       <c r="J94" t="s">
         <v>49</v>
       </c>
       <c r="K94">
-        <f t="shared" ref="K94:K97" si="20">(B85-K85)/SQRT(K85)</f>
-        <v>1.1678309891599041</v>
+        <f t="shared" ref="K94:K97" si="26">(B85-K85)/SQRT(K85*(1-$H85/$H$89)*(1-B$89/$H$89))</f>
+        <v>1.7307060849464544</v>
       </c>
       <c r="L94">
-        <f t="shared" si="17"/>
-        <v>0.39401566310329361</v>
+        <f t="shared" si="25"/>
+        <v>0.53669167151937391</v>
       </c>
       <c r="M94">
-        <f t="shared" si="17"/>
-        <v>-1.3296164804516342</v>
+        <f t="shared" si="25"/>
+        <v>-1.6823839916205392</v>
       </c>
       <c r="N94">
-        <f t="shared" si="17"/>
-        <v>-1.1475190465588947</v>
+        <f t="shared" si="25"/>
+        <v>-1.5094993557334204</v>
       </c>
       <c r="O94">
-        <f t="shared" si="17"/>
-        <v>-0.40716111374923031</v>
+        <f t="shared" si="25"/>
+        <v>-0.54771972015889991</v>
       </c>
       <c r="P94">
-        <f t="shared" si="17"/>
-        <v>0.66121482107479035</v>
+        <f t="shared" si="25"/>
+        <v>0.8226683547258673</v>
       </c>
     </row>
     <row r="95" spans="1:16" x14ac:dyDescent="0.25">
@@ -4999,55 +5356,55 @@
         <v>50</v>
       </c>
       <c r="B95">
-        <f t="shared" si="18"/>
+        <f t="shared" si="24"/>
         <v>0.31943170819463329</v>
       </c>
       <c r="C95">
-        <f t="shared" si="19"/>
+        <f t="shared" si="24"/>
         <v>8.4256717494539963E-3</v>
       </c>
       <c r="D95">
-        <f t="shared" si="16"/>
+        <f t="shared" si="24"/>
         <v>1.9482666330803807E-2</v>
       </c>
       <c r="E95">
-        <f t="shared" si="16"/>
+        <f t="shared" si="24"/>
         <v>4.0650625548134913</v>
       </c>
       <c r="F95">
-        <f t="shared" si="16"/>
+        <f t="shared" si="24"/>
         <v>0.42559930701874699</v>
       </c>
       <c r="G95">
-        <f t="shared" si="16"/>
+        <f t="shared" si="24"/>
         <v>0.59416396851084186</v>
       </c>
       <c r="J95" t="s">
         <v>50</v>
       </c>
       <c r="K95">
-        <f t="shared" si="20"/>
-        <v>0.56518289800261412</v>
+        <f t="shared" si="26"/>
+        <v>0.89840653026524542</v>
       </c>
       <c r="L95">
-        <f t="shared" si="17"/>
-        <v>9.1791457932936193E-2</v>
+        <f t="shared" si="25"/>
+        <v>0.13410785002587425</v>
       </c>
       <c r="M95">
-        <f t="shared" si="17"/>
-        <v>-0.13958032214751406</v>
+        <f t="shared" si="25"/>
+        <v>-0.18943642835292535</v>
       </c>
       <c r="N95">
-        <f t="shared" si="17"/>
-        <v>-2.0162000284727433</v>
+        <f t="shared" si="25"/>
+        <v>-2.8447703227133907</v>
       </c>
       <c r="O95">
-        <f t="shared" si="17"/>
-        <v>0.65237972609420281</v>
+        <f t="shared" si="25"/>
+        <v>0.94131093284436518</v>
       </c>
       <c r="P95">
-        <f t="shared" si="17"/>
-        <v>0.77082032180712634</v>
+        <f t="shared" si="25"/>
+        <v>1.0286696599394156</v>
       </c>
     </row>
     <row r="96" spans="1:16" x14ac:dyDescent="0.25">
@@ -5055,55 +5412,55 @@
         <v>51</v>
       </c>
       <c r="B96">
-        <f t="shared" si="18"/>
+        <f t="shared" si="24"/>
         <v>8.1996622510139403</v>
       </c>
       <c r="C96">
-        <f t="shared" si="19"/>
+        <f t="shared" si="24"/>
         <v>7.4269340974212037</v>
       </c>
       <c r="D96">
-        <f t="shared" si="16"/>
+        <f t="shared" si="24"/>
         <v>12.932895006139994</v>
       </c>
       <c r="E96">
-        <f t="shared" si="16"/>
+        <f t="shared" si="24"/>
         <v>21.090392574633263</v>
       </c>
       <c r="F96">
-        <f t="shared" si="16"/>
+        <f t="shared" si="24"/>
         <v>0.78564029094115062</v>
       </c>
       <c r="G96">
-        <f t="shared" si="16"/>
+        <f t="shared" si="24"/>
         <v>1.7535816618911173</v>
       </c>
       <c r="J96" t="s">
         <v>51</v>
       </c>
       <c r="K96">
-        <f t="shared" si="20"/>
-        <v>-2.8635052385169368</v>
+        <f t="shared" si="26"/>
+        <v>-3.6926939207568199</v>
       </c>
       <c r="L96">
-        <f t="shared" si="17"/>
-        <v>-2.7252401907760722</v>
+        <f t="shared" si="25"/>
+        <v>-3.2301162957854803</v>
       </c>
       <c r="M96">
-        <f t="shared" si="17"/>
-        <v>3.5962334471137987</v>
+        <f t="shared" si="25"/>
+        <v>3.9595754044599434</v>
       </c>
       <c r="N96">
-        <f t="shared" si="17"/>
-        <v>4.5924277429953397</v>
+        <f t="shared" si="25"/>
+        <v>5.2567505085942825</v>
       </c>
       <c r="O96">
-        <f t="shared" si="17"/>
-        <v>0.88636352076399816</v>
+        <f t="shared" si="25"/>
+        <v>1.0375426592668091</v>
       </c>
       <c r="P96">
-        <f t="shared" si="17"/>
-        <v>-1.3242287045261925</v>
+        <f>(G87-P87)/SQRT(P87*(1-$H87/$H$89)*(1-G$89/$H$89))</f>
+        <v>-1.4336634516664148</v>
       </c>
     </row>
     <row r="97" spans="1:16" x14ac:dyDescent="0.25">
@@ -5111,27 +5468,27 @@
         <v>52</v>
       </c>
       <c r="B97">
-        <f t="shared" si="18"/>
+        <f t="shared" si="24"/>
         <v>3.7006531527523174</v>
       </c>
       <c r="C97">
-        <f t="shared" si="19"/>
+        <f t="shared" si="24"/>
         <v>8.4122435984900212E-2</v>
       </c>
       <c r="D97">
-        <f t="shared" si="16"/>
+        <f t="shared" si="24"/>
         <v>1.312496345242966E-2</v>
       </c>
       <c r="E97">
-        <f t="shared" si="16"/>
+        <f t="shared" si="24"/>
         <v>8.8280865266538608</v>
       </c>
       <c r="F97">
-        <f t="shared" si="16"/>
+        <f t="shared" si="24"/>
         <v>4.1262004471173536E-2</v>
       </c>
       <c r="G97">
-        <f t="shared" si="16"/>
+        <f t="shared" si="24"/>
         <v>0.29142568202065922</v>
       </c>
       <c r="H97" t="s">
@@ -5141,28 +5498,28 @@
         <v>52</v>
       </c>
       <c r="K97">
-        <f t="shared" si="20"/>
-        <v>-1.9237081776486571</v>
+        <f t="shared" si="26"/>
+        <v>-2.476805283211045</v>
       </c>
       <c r="L97">
-        <f t="shared" si="17"/>
-        <v>0.29003868015301032</v>
+        <f t="shared" si="25"/>
+        <v>0.34322320195023737</v>
       </c>
       <c r="M97">
-        <f t="shared" si="17"/>
-        <v>0.11456423286711111</v>
+        <f t="shared" si="25"/>
+        <v>0.12593810034321021</v>
       </c>
       <c r="N97">
-        <f t="shared" si="17"/>
-        <v>2.9712096066507763</v>
+        <f t="shared" si="25"/>
+        <v>3.3955933067103601</v>
       </c>
       <c r="O97">
-        <f t="shared" si="17"/>
-        <v>-0.20313051093120782</v>
+        <f t="shared" si="25"/>
+        <v>-0.23739774742805125</v>
       </c>
       <c r="P97">
-        <f t="shared" si="17"/>
-        <v>-0.53983857033437244</v>
+        <f t="shared" si="25"/>
+        <v>-0.58351963166487852</v>
       </c>
     </row>
     <row r="98" spans="1:16" x14ac:dyDescent="0.25">
@@ -5180,23 +5537,23 @@
         <v>17.461427713223554</v>
       </c>
       <c r="C99">
-        <f t="shared" ref="C99:G99" si="21">SUM(C93:C97)</f>
+        <f t="shared" ref="C99:G99" si="27">SUM(C93:C97)</f>
         <v>11.490368395191764</v>
       </c>
       <c r="D99">
-        <f t="shared" si="21"/>
+        <f t="shared" si="27"/>
         <v>16.578654827315543</v>
       </c>
       <c r="E99">
-        <f t="shared" si="21"/>
+        <f t="shared" si="27"/>
         <v>38.727275715737257</v>
       </c>
       <c r="F99">
-        <f t="shared" si="21"/>
+        <f t="shared" si="27"/>
         <v>3.9353942128106008</v>
       </c>
       <c r="G99">
-        <f t="shared" si="21"/>
+        <f t="shared" si="27"/>
         <v>4.1967201915731325</v>
       </c>
     </row>
@@ -5205,21 +5562,24 @@
         <v>72</v>
       </c>
       <c r="B102" t="s">
+        <v>80</v>
+      </c>
+      <c r="C102" t="s">
         <v>0</v>
       </c>
-      <c r="C102" t="s">
+      <c r="D102" t="s">
         <v>2</v>
       </c>
-      <c r="D102" t="s">
+      <c r="E102" t="s">
         <v>63</v>
       </c>
-      <c r="E102" t="s">
+      <c r="F102" t="s">
         <v>64</v>
       </c>
-      <c r="F102" t="s">
+      <c r="G102" t="s">
         <v>65</v>
       </c>
-      <c r="G102" t="s">
+      <c r="H102" t="s">
         <v>66</v>
       </c>
     </row>
@@ -5227,115 +5587,130 @@
       <c r="A103" t="s">
         <v>48</v>
       </c>
-      <c r="B103" s="6">
-        <v>1.9692260870759517</v>
+      <c r="B103" t="s">
+        <v>48</v>
       </c>
       <c r="C103" s="6">
-        <v>1.9533657740590928</v>
+        <v>2.4883088180994499</v>
       </c>
       <c r="D103" s="6">
-        <v>-1.3584079675501484</v>
+        <v>2.2686124772108611</v>
       </c>
       <c r="E103" s="6">
-        <v>-1.8511980168045783</v>
+        <v>-1.4655287105051573</v>
       </c>
       <c r="F103" s="6">
-        <v>-1.5865410293560063</v>
+        <v>-2.0763056158551207</v>
       </c>
       <c r="G103" s="6">
-        <v>-1.0584629608737128</v>
+        <v>-1.8197375833118294</v>
+      </c>
+      <c r="H103" s="6">
+        <v>-1.122853896195074</v>
       </c>
     </row>
     <row r="104" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A104" t="s">
         <v>49</v>
       </c>
-      <c r="B104" s="6">
-        <v>1.1678309891599041</v>
+      <c r="B104" t="s">
+        <v>49</v>
       </c>
       <c r="C104" s="6">
-        <v>0.39401566310329361</v>
+        <v>1.7307060849464544</v>
       </c>
       <c r="D104" s="6">
-        <v>-1.3296164804516342</v>
+        <v>0.53669167151937391</v>
       </c>
       <c r="E104" s="6">
-        <v>-1.1475190465588947</v>
+        <v>-1.6823839916205392</v>
       </c>
       <c r="F104" s="6">
-        <v>-0.40716111374923031</v>
+        <v>-1.5094993557334204</v>
       </c>
       <c r="G104" s="6">
-        <v>0.66121482107479035</v>
+        <v>-0.54771972015889991</v>
+      </c>
+      <c r="H104" s="6">
+        <v>0.8226683547258673</v>
       </c>
     </row>
     <row r="105" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A105" t="s">
         <v>50</v>
       </c>
-      <c r="B105" s="6">
-        <v>0.56518289800261412</v>
+      <c r="B105" t="s">
+        <v>50</v>
       </c>
       <c r="C105" s="6">
-        <v>9.1791457932936193E-2</v>
+        <v>0.89840653026524542</v>
       </c>
       <c r="D105" s="6">
-        <v>-0.13958032214751406</v>
+        <v>0.13410785002587425</v>
       </c>
       <c r="E105" s="6">
-        <v>-2.0162000284727433</v>
+        <v>-0.18943642835292535</v>
       </c>
       <c r="F105" s="6">
-        <v>0.65237972609420281</v>
+        <v>-2.8447703227133907</v>
       </c>
       <c r="G105" s="6">
-        <v>0.77082032180712634</v>
+        <v>0.94131093284436518</v>
+      </c>
+      <c r="H105" s="6">
+        <v>1.0286696599394156</v>
       </c>
     </row>
     <row r="106" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A106" t="s">
         <v>51</v>
       </c>
-      <c r="B106" s="6">
-        <v>-2.8635052385169368</v>
+      <c r="B106" t="s">
+        <v>51</v>
       </c>
       <c r="C106" s="6">
-        <v>-2.7252401907760722</v>
+        <v>-3.6926939207568199</v>
       </c>
       <c r="D106" s="6">
-        <v>3.5962334471137987</v>
+        <v>-3.2301162957854803</v>
       </c>
       <c r="E106" s="6">
-        <v>4.5924277429953397</v>
+        <v>3.9595754044599434</v>
       </c>
       <c r="F106" s="6">
-        <v>0.88636352076399816</v>
+        <v>5.2567505085942825</v>
       </c>
       <c r="G106" s="6">
-        <v>-1.3242287045261925</v>
+        <v>1.0375426592668091</v>
+      </c>
+      <c r="H106" s="6">
+        <v>-1.4336634516664148</v>
       </c>
     </row>
     <row r="107" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A107" t="s">
         <v>74</v>
       </c>
-      <c r="B107" s="6">
-        <v>-1.9237081776486571</v>
+      <c r="B107" t="s">
+        <v>52</v>
       </c>
       <c r="C107" s="6">
-        <v>0.29003868015301032</v>
+        <v>-2.476805283211045</v>
       </c>
       <c r="D107" s="6">
-        <v>0.11456423286711111</v>
+        <v>0.34322320195023737</v>
       </c>
       <c r="E107" s="6">
-        <v>2.9712096066507763</v>
+        <v>0.12593810034321021</v>
       </c>
       <c r="F107" s="6">
-        <v>-0.20313051093120782</v>
+        <v>3.3955933067103601</v>
       </c>
       <c r="G107" s="6">
-        <v>-0.53983857033437244</v>
+        <v>-0.23739774742805125</v>
+      </c>
+      <c r="H107" s="6">
+        <v>-0.58351963166487852</v>
       </c>
     </row>
     <row r="111" spans="1:16" x14ac:dyDescent="0.25">
@@ -5416,23 +5791,23 @@
         <v>9.844537815126051</v>
       </c>
       <c r="L112">
-        <f t="shared" ref="L112:P117" si="22">$H112*C$118/$H$118</f>
+        <f t="shared" ref="L112:P117" si="28">$H112*C$118/$H$118</f>
         <v>14.021008403361344</v>
       </c>
       <c r="M112">
-        <f t="shared" si="22"/>
+        <f t="shared" si="28"/>
         <v>13.42436974789916</v>
       </c>
       <c r="N112">
-        <f t="shared" si="22"/>
+        <f t="shared" si="28"/>
         <v>12.827731092436975</v>
       </c>
       <c r="O112">
-        <f t="shared" si="22"/>
+        <f t="shared" si="28"/>
         <v>18.794117647058822</v>
       </c>
       <c r="P112">
-        <f t="shared" si="22"/>
+        <f t="shared" si="28"/>
         <v>2.0882352941176472</v>
       </c>
     </row>
@@ -5459,34 +5834,34 @@
         <v>0</v>
       </c>
       <c r="H113">
-        <f t="shared" ref="H113:H117" si="23">SUM(B113:G113)</f>
+        <f t="shared" ref="H113:H117" si="29">SUM(B113:G113)</f>
         <v>7</v>
       </c>
       <c r="J113" t="s">
         <v>55</v>
       </c>
       <c r="K113">
-        <f t="shared" ref="K113:K117" si="24">$H113*B$118/$H$118</f>
+        <f t="shared" ref="K113:K116" si="30">$H113*B$118/$H$118</f>
         <v>0.97058823529411764</v>
       </c>
       <c r="L113">
-        <f t="shared" si="22"/>
+        <f t="shared" si="28"/>
         <v>1.3823529411764706</v>
       </c>
       <c r="M113">
-        <f t="shared" si="22"/>
+        <f t="shared" si="28"/>
         <v>1.3235294117647058</v>
       </c>
       <c r="N113">
-        <f t="shared" si="22"/>
+        <f t="shared" si="28"/>
         <v>1.2647058823529411</v>
       </c>
       <c r="O113">
-        <f t="shared" si="22"/>
+        <f t="shared" si="28"/>
         <v>1.8529411764705883</v>
       </c>
       <c r="P113">
-        <f t="shared" si="22"/>
+        <f t="shared" si="28"/>
         <v>0.20588235294117646</v>
       </c>
     </row>
@@ -5513,34 +5888,34 @@
         <v>1</v>
       </c>
       <c r="H114">
-        <f t="shared" si="23"/>
+        <f t="shared" si="29"/>
         <v>116</v>
       </c>
       <c r="J114" t="s">
         <v>56</v>
       </c>
       <c r="K114">
-        <f t="shared" si="24"/>
+        <f t="shared" si="30"/>
         <v>16.084033613445378</v>
       </c>
       <c r="L114">
-        <f t="shared" si="22"/>
+        <f t="shared" si="28"/>
         <v>22.907563025210084</v>
       </c>
       <c r="M114">
-        <f t="shared" si="22"/>
+        <f t="shared" si="28"/>
         <v>21.932773109243698</v>
       </c>
       <c r="N114">
-        <f t="shared" si="22"/>
+        <f t="shared" si="28"/>
         <v>20.957983193277311</v>
       </c>
       <c r="O114">
-        <f t="shared" si="22"/>
+        <f t="shared" si="28"/>
         <v>30.705882352941178</v>
       </c>
       <c r="P114">
-        <f t="shared" si="22"/>
+        <f t="shared" si="28"/>
         <v>3.4117647058823528</v>
       </c>
     </row>
@@ -5564,38 +5939,38 @@
         <v>0</v>
       </c>
       <c r="G115">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="H115">
-        <f t="shared" si="23"/>
-        <v>21</v>
+        <f t="shared" si="29"/>
+        <v>24</v>
       </c>
       <c r="J115" t="s">
         <v>57</v>
       </c>
       <c r="K115">
-        <f t="shared" si="24"/>
-        <v>2.9117647058823528</v>
+        <f t="shared" si="30"/>
+        <v>3.327731092436975</v>
       </c>
       <c r="L115">
-        <f t="shared" si="22"/>
-        <v>4.1470588235294121</v>
+        <f t="shared" si="28"/>
+        <v>4.7394957983193278</v>
       </c>
       <c r="M115">
-        <f t="shared" si="22"/>
-        <v>3.9705882352941178</v>
+        <f t="shared" si="28"/>
+        <v>4.53781512605042</v>
       </c>
       <c r="N115">
-        <f t="shared" si="22"/>
-        <v>3.7941176470588234</v>
+        <f t="shared" si="28"/>
+        <v>4.3361344537815123</v>
       </c>
       <c r="O115">
-        <f t="shared" si="22"/>
-        <v>5.5588235294117645</v>
+        <f t="shared" si="28"/>
+        <v>6.3529411764705879</v>
       </c>
       <c r="P115">
-        <f t="shared" si="22"/>
-        <v>0.61764705882352944</v>
+        <f t="shared" si="28"/>
+        <v>0.70588235294117652</v>
       </c>
     </row>
     <row r="116" spans="1:16" x14ac:dyDescent="0.25">
@@ -5621,34 +5996,34 @@
         <v>0</v>
       </c>
       <c r="H116">
-        <f t="shared" si="23"/>
+        <f t="shared" si="29"/>
         <v>19</v>
       </c>
       <c r="J116" t="s">
         <v>58</v>
       </c>
       <c r="K116">
-        <f t="shared" si="24"/>
+        <f t="shared" si="30"/>
         <v>2.634453781512605</v>
       </c>
       <c r="L116">
-        <f t="shared" si="22"/>
+        <f t="shared" si="28"/>
         <v>3.7521008403361344</v>
       </c>
       <c r="M116">
-        <f t="shared" si="22"/>
+        <f t="shared" si="28"/>
         <v>3.5924369747899161</v>
       </c>
       <c r="N116">
-        <f t="shared" si="22"/>
+        <f t="shared" si="28"/>
         <v>3.4327731092436973</v>
       </c>
       <c r="O116">
-        <f t="shared" si="22"/>
+        <f t="shared" si="28"/>
         <v>5.0294117647058822</v>
       </c>
       <c r="P116">
-        <f t="shared" si="22"/>
+        <f t="shared" si="28"/>
         <v>0.55882352941176472</v>
       </c>
     </row>
@@ -5672,38 +6047,38 @@
         <v>1</v>
       </c>
       <c r="G117">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="H117">
-        <f t="shared" si="23"/>
-        <v>4</v>
+        <f t="shared" si="29"/>
+        <v>1</v>
       </c>
       <c r="J117" t="s">
-        <v>59</v>
+        <v>79</v>
       </c>
       <c r="K117">
-        <f t="shared" si="24"/>
-        <v>0.55462184873949583</v>
+        <f>$H117*B$118/$H$118</f>
+        <v>0.13865546218487396</v>
       </c>
       <c r="L117">
-        <f t="shared" si="22"/>
-        <v>0.78991596638655459</v>
+        <f t="shared" si="28"/>
+        <v>0.19747899159663865</v>
       </c>
       <c r="M117">
-        <f t="shared" si="22"/>
-        <v>0.75630252100840334</v>
+        <f t="shared" si="28"/>
+        <v>0.18907563025210083</v>
       </c>
       <c r="N117">
-        <f t="shared" si="22"/>
-        <v>0.72268907563025209</v>
+        <f t="shared" si="28"/>
+        <v>0.18067226890756302</v>
       </c>
       <c r="O117">
-        <f t="shared" si="22"/>
-        <v>1.0588235294117647</v>
+        <f t="shared" si="28"/>
+        <v>0.26470588235294118</v>
       </c>
       <c r="P117">
-        <f t="shared" si="22"/>
-        <v>0.11764705882352941</v>
+        <f t="shared" si="28"/>
+        <v>2.9411764705882353E-2</v>
       </c>
     </row>
     <row r="118" spans="1:16" x14ac:dyDescent="0.25">
@@ -5715,23 +6090,23 @@
         <v>33</v>
       </c>
       <c r="C118">
-        <f t="shared" ref="C118:G118" si="25">SUM(C112:C117)</f>
+        <f t="shared" ref="C118:G118" si="31">SUM(C112:C117)</f>
         <v>47</v>
       </c>
       <c r="D118">
-        <f t="shared" si="25"/>
+        <f t="shared" si="31"/>
         <v>45</v>
       </c>
       <c r="E118">
-        <f t="shared" si="25"/>
+        <f t="shared" si="31"/>
         <v>43</v>
       </c>
       <c r="F118">
-        <f t="shared" si="25"/>
+        <f t="shared" si="31"/>
         <v>63</v>
       </c>
       <c r="G118">
-        <f t="shared" si="25"/>
+        <f t="shared" si="31"/>
         <v>7</v>
       </c>
       <c r="H118">
@@ -5792,51 +6167,51 @@
         <v>3.8488058475630962</v>
       </c>
       <c r="C122">
-        <f t="shared" ref="C122:G127" si="26">((C112-L112)^2)/L112</f>
+        <f t="shared" ref="C122:G127" si="32">((C112-L112)^2)/L112</f>
         <v>3.4738103212516651</v>
       </c>
       <c r="D122">
-        <f t="shared" si="26"/>
+        <f t="shared" si="32"/>
         <v>2.1918188871792852</v>
       </c>
       <c r="E122">
-        <f t="shared" si="26"/>
+        <f t="shared" si="32"/>
         <v>3.6341510072748395</v>
       </c>
       <c r="F122">
-        <f t="shared" si="26"/>
+        <f t="shared" si="32"/>
         <v>7.7372733130811139E-2</v>
       </c>
       <c r="G122">
-        <f t="shared" si="26"/>
+        <f t="shared" si="32"/>
         <v>2.0882352941176472</v>
       </c>
       <c r="J122" t="s">
         <v>54</v>
       </c>
       <c r="K122">
-        <f>(B112-K112)/SQRT(K112)</f>
-        <v>1.9618373652173864</v>
+        <f>(B112-K112)/SQRT(K112*(1-$H112/$H$118)*(1-B$118/$H$118))</f>
+        <v>2.5235086214445861</v>
       </c>
       <c r="L122">
-        <f t="shared" ref="L122:P127" si="27">(C112-L112)/SQRT(L112)</f>
-        <v>1.8638160642219139</v>
+        <f t="shared" ref="L122:P127" si="33">(C112-L112)/SQRT(L112*(1-$H112/$H$118)*(1-C$118/$H$118))</f>
+        <v>2.4837340344014081</v>
       </c>
       <c r="M122">
-        <f t="shared" si="27"/>
-        <v>-1.4804792761735253</v>
+        <f t="shared" si="33"/>
+        <v>-1.9626479249720317</v>
       </c>
       <c r="N122">
-        <f t="shared" si="27"/>
-        <v>-1.9063449339704606</v>
+        <f t="shared" si="33"/>
+        <v>-2.5142178213244453</v>
       </c>
       <c r="O122">
-        <f t="shared" si="27"/>
-        <v>0.2781595461795463</v>
+        <f t="shared" si="33"/>
+        <v>0.3872519972059611</v>
       </c>
       <c r="P122">
-        <f t="shared" si="27"/>
-        <v>-1.4450727642986172</v>
+        <f t="shared" si="33"/>
+        <v>-1.7510657252129647</v>
       </c>
     </row>
     <row r="123" spans="1:16" x14ac:dyDescent="0.25">
@@ -5844,55 +6219,55 @@
         <v>55</v>
       </c>
       <c r="B123">
-        <f t="shared" ref="B123:B127" si="28">((B113-K113)^2)/K113</f>
+        <f t="shared" ref="B123:B127" si="34">((B113-K113)^2)/K113</f>
         <v>4.2433155080213893</v>
       </c>
       <c r="C123">
-        <f t="shared" si="26"/>
+        <f t="shared" si="32"/>
         <v>0.10575719649561952</v>
       </c>
       <c r="D123">
-        <f t="shared" si="26"/>
+        <f t="shared" si="32"/>
         <v>7.9084967320261421E-2</v>
       </c>
       <c r="E123">
-        <f t="shared" si="26"/>
+        <f t="shared" si="32"/>
         <v>1.2647058823529411</v>
       </c>
       <c r="F123">
-        <f t="shared" si="26"/>
+        <f t="shared" si="32"/>
         <v>1.1671335200746953E-2</v>
       </c>
       <c r="G123">
-        <f t="shared" si="26"/>
+        <f t="shared" si="32"/>
         <v>0.20588235294117646</v>
       </c>
       <c r="J123" t="s">
         <v>55</v>
       </c>
       <c r="K123">
-        <f t="shared" ref="K123:K127" si="29">(B113-K113)/SQRT(K113)</f>
-        <v>2.0599309473915355</v>
+        <f t="shared" ref="K123:K127" si="35">(B113-K113)/SQRT(K113*(1-$H113/$H$118)*(1-B$118/$H$118))</f>
+        <v>2.2529248162725399</v>
       </c>
       <c r="L123">
-        <f t="shared" si="27"/>
-        <v>-0.32520331562826899</v>
+        <f t="shared" si="33"/>
+        <v>-0.36847603576441651</v>
       </c>
       <c r="M123">
-        <f t="shared" si="27"/>
-        <v>-0.28122049591070247</v>
+        <f t="shared" si="33"/>
+        <v>-0.31698541664525309</v>
       </c>
       <c r="N123">
-        <f t="shared" si="27"/>
-        <v>-1.124591429076774</v>
+        <f t="shared" si="33"/>
+        <v>-1.2610968203770836</v>
       </c>
       <c r="O123">
-        <f t="shared" si="27"/>
-        <v>0.10803395392536067</v>
+        <f t="shared" si="33"/>
+        <v>0.127882822748078</v>
       </c>
       <c r="P123">
-        <f t="shared" si="27"/>
-        <v>-0.4537426064865151</v>
+        <f t="shared" si="33"/>
+        <v>-0.46749238244065189</v>
       </c>
     </row>
     <row r="124" spans="1:16" x14ac:dyDescent="0.25">
@@ -5900,55 +6275,55 @@
         <v>56</v>
       </c>
       <c r="B124">
-        <f t="shared" si="28"/>
+        <f t="shared" si="34"/>
         <v>6.3222781275519608</v>
       </c>
       <c r="C124">
-        <f t="shared" si="26"/>
+        <f t="shared" si="32"/>
         <v>7.2729335314463279</v>
       </c>
       <c r="D124">
-        <f t="shared" si="26"/>
+        <f t="shared" si="32"/>
         <v>2.2772175536881418</v>
       </c>
       <c r="E124">
-        <f t="shared" si="26"/>
+        <f t="shared" si="32"/>
         <v>6.919089849251649</v>
       </c>
       <c r="F124">
-        <f t="shared" si="26"/>
+        <f t="shared" si="32"/>
         <v>1.2901735406806396</v>
       </c>
       <c r="G124">
-        <f t="shared" si="26"/>
+        <f t="shared" si="32"/>
         <v>1.7048681541582149</v>
       </c>
       <c r="J124" t="s">
         <v>56</v>
       </c>
       <c r="K124">
-        <f t="shared" si="29"/>
-        <v>-2.5144140724136825</v>
+        <f t="shared" si="35"/>
+        <v>-3.7840503796027849</v>
       </c>
       <c r="L124">
-        <f t="shared" si="27"/>
-        <v>-2.6968376909718406</v>
+        <f t="shared" si="33"/>
+        <v>-4.2047014761183785</v>
       </c>
       <c r="M124">
-        <f t="shared" si="27"/>
-        <v>1.5090452457392198</v>
+        <f t="shared" si="33"/>
+        <v>2.3405646884596703</v>
       </c>
       <c r="N124">
-        <f t="shared" si="27"/>
-        <v>2.630416288204521</v>
+        <f t="shared" si="33"/>
+        <v>4.0588613969278144</v>
       </c>
       <c r="O124">
-        <f t="shared" si="27"/>
-        <v>1.1358580636156261</v>
+        <f t="shared" si="33"/>
+        <v>1.8501293079477246</v>
       </c>
       <c r="P124">
-        <f t="shared" si="27"/>
-        <v>-1.3057059983618879</v>
+        <f t="shared" si="33"/>
+        <v>-1.851128004510501</v>
       </c>
     </row>
     <row r="125" spans="1:16" x14ac:dyDescent="0.25">
@@ -5956,55 +6331,55 @@
         <v>57</v>
       </c>
       <c r="B125">
-        <f t="shared" si="28"/>
-        <v>0.28550207961972662</v>
+        <f t="shared" si="34"/>
+        <v>0.52975129445717695</v>
       </c>
       <c r="C125">
-        <f t="shared" si="26"/>
-        <v>0.82790988735919857</v>
+        <f t="shared" si="32"/>
+        <v>0.33524047917039151</v>
       </c>
       <c r="D125">
-        <f t="shared" si="26"/>
-        <v>1.0372549019607842</v>
+        <f t="shared" si="32"/>
+        <v>0.47114845938375355</v>
       </c>
       <c r="E125">
         <f>((E115-N115)^2)/N115</f>
-        <v>1.1171910624715019E-2</v>
+        <v>2.6056934401667599E-2</v>
       </c>
       <c r="F125">
-        <f t="shared" si="26"/>
-        <v>5.5588235294117645</v>
+        <f t="shared" si="32"/>
+        <v>6.3529411764705879</v>
       </c>
       <c r="G125">
-        <f t="shared" si="26"/>
-        <v>9.1890756302521002</v>
+        <f t="shared" si="32"/>
+        <v>39.705882352941174</v>
       </c>
       <c r="J125" t="s">
         <v>57</v>
       </c>
       <c r="K125">
-        <f t="shared" si="29"/>
-        <v>-0.53432394632818636</v>
+        <f t="shared" si="35"/>
+        <v>-0.82704502425821391</v>
       </c>
       <c r="L125">
-        <f t="shared" si="27"/>
-        <v>0.90989553650910848</v>
+        <f t="shared" si="33"/>
+        <v>0.68160318812038334</v>
       </c>
       <c r="M125">
-        <f t="shared" si="27"/>
-        <v>1.0184571183711095</v>
+        <f t="shared" si="33"/>
+        <v>0.80384127743952682</v>
       </c>
       <c r="N125">
-        <f t="shared" si="27"/>
-        <v>0.10569725930559894</v>
+        <f t="shared" si="33"/>
+        <v>-0.18806779145509095</v>
       </c>
       <c r="O125">
-        <f t="shared" si="27"/>
-        <v>-2.3577157439801271</v>
+        <f t="shared" si="33"/>
+        <v>-3.0998341830841243</v>
       </c>
       <c r="P125">
-        <f t="shared" si="27"/>
-        <v>3.0313488136887345</v>
+        <f t="shared" si="33"/>
+        <v>6.7451483555328728</v>
       </c>
     </row>
     <row r="126" spans="1:16" x14ac:dyDescent="0.25">
@@ -6012,55 +6387,55 @@
         <v>58</v>
       </c>
       <c r="B126">
-        <f t="shared" si="28"/>
+        <f t="shared" si="34"/>
         <v>4.299525551847533</v>
       </c>
       <c r="C126">
-        <f t="shared" si="26"/>
+        <f t="shared" si="32"/>
         <v>7.3400067753865272</v>
       </c>
       <c r="D126">
-        <f t="shared" si="26"/>
+        <f t="shared" si="32"/>
         <v>1.8707995478893313</v>
       </c>
       <c r="E126">
-        <f t="shared" si="26"/>
+        <f t="shared" si="32"/>
         <v>3.4327731092436973</v>
       </c>
       <c r="F126">
-        <f t="shared" si="26"/>
+        <f t="shared" si="32"/>
         <v>0.81888544891640858</v>
       </c>
       <c r="G126">
-        <f t="shared" si="26"/>
+        <f t="shared" si="32"/>
         <v>0.55882352941176472</v>
       </c>
       <c r="J126" t="s">
         <v>58</v>
       </c>
       <c r="K126">
-        <f t="shared" si="29"/>
-        <v>2.0735297325689674</v>
+        <f t="shared" si="35"/>
+        <v>2.3291005409264507</v>
       </c>
       <c r="L126">
-        <f t="shared" si="27"/>
-        <v>2.7092446872489253</v>
+        <f t="shared" si="33"/>
+        <v>3.1527275832000812</v>
       </c>
       <c r="M126">
-        <f t="shared" si="27"/>
-        <v>-1.3677717455369998</v>
+        <f t="shared" si="33"/>
+        <v>-1.5833972023830365</v>
       </c>
       <c r="N126">
-        <f t="shared" si="27"/>
-        <v>-1.8527744356083116</v>
+        <f t="shared" si="33"/>
+        <v>-2.133831606720658</v>
       </c>
       <c r="O126">
-        <f t="shared" si="27"/>
-        <v>-0.90492289666932879</v>
+        <f t="shared" si="33"/>
+        <v>-1.1001387253853605</v>
       </c>
       <c r="P126">
-        <f t="shared" si="27"/>
-        <v>-0.74754500159640203</v>
+        <f t="shared" si="33"/>
+        <v>-0.79101779136571349</v>
       </c>
     </row>
     <row r="127" spans="1:16" x14ac:dyDescent="0.25">
@@ -6068,254 +6443,275 @@
         <v>59</v>
       </c>
       <c r="B127">
-        <f t="shared" si="28"/>
-        <v>0.55462184873949583</v>
+        <f t="shared" si="34"/>
+        <v>0.13865546218487396</v>
       </c>
       <c r="C127">
-        <f t="shared" si="26"/>
-        <v>0.78991596638655448</v>
+        <f t="shared" si="32"/>
+        <v>0.19747899159663862</v>
       </c>
       <c r="D127">
-        <f t="shared" si="26"/>
-        <v>0.75630252100840334</v>
+        <f t="shared" si="32"/>
+        <v>0.18907563025210083</v>
       </c>
       <c r="E127">
-        <f t="shared" si="26"/>
-        <v>0.72268907563025209</v>
+        <f t="shared" si="32"/>
+        <v>0.18067226890756302</v>
       </c>
       <c r="F127">
-        <f t="shared" si="26"/>
-        <v>3.2679738562091517E-3</v>
+        <f t="shared" si="32"/>
+        <v>2.0424836601307192</v>
       </c>
       <c r="G127">
-        <f t="shared" si="26"/>
-        <v>70.617647058823536</v>
+        <f t="shared" si="32"/>
+        <v>2.9411764705882353E-2</v>
       </c>
       <c r="H127" t="s">
         <v>70</v>
       </c>
       <c r="J127" t="s">
-        <v>59</v>
+        <v>79</v>
       </c>
       <c r="K127">
-        <f t="shared" si="29"/>
-        <v>-0.74472937953292517</v>
+        <f t="shared" si="35"/>
+        <v>-0.40206321858408139</v>
       </c>
       <c r="L127">
-        <f t="shared" si="27"/>
-        <v>-0.88877216787349644</v>
+        <f t="shared" si="33"/>
+        <v>-0.49710319088589316</v>
       </c>
       <c r="M127">
-        <f t="shared" si="27"/>
-        <v>-0.86965655347867254</v>
+        <f t="shared" si="33"/>
+        <v>-0.48388471959081264</v>
       </c>
       <c r="N127">
-        <f t="shared" si="27"/>
-        <v>-0.85011121368339337</v>
+        <f t="shared" si="33"/>
+        <v>-0.47057757527813282</v>
       </c>
       <c r="O127">
-        <f t="shared" si="27"/>
-        <v>-5.7166195047502949E-2</v>
+        <f t="shared" si="33"/>
+        <v>1.670179139828603</v>
       </c>
       <c r="P127">
-        <f t="shared" si="27"/>
-        <v>8.4034306719829317</v>
+        <f t="shared" si="33"/>
+        <v>-0.17444452181248013</v>
       </c>
     </row>
     <row r="128" spans="1:16" x14ac:dyDescent="0.25">
       <c r="H128">
         <f>SUM(B129:G129)</f>
-        <v>155.68616843599443</v>
-      </c>
-    </row>
-    <row r="129" spans="1:7" x14ac:dyDescent="0.25">
+        <v>115.53078452692421</v>
+      </c>
+    </row>
+    <row r="129" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A129" t="s">
         <v>15</v>
       </c>
       <c r="B129">
         <f>SUM(B122:B127)</f>
-        <v>19.554048963343202</v>
+        <v>19.382331791626033</v>
       </c>
       <c r="C129">
-        <f t="shared" ref="C129:G129" si="30">SUM(C122:C127)</f>
-        <v>19.810333678325893</v>
+        <f t="shared" ref="C129:G129" si="36">SUM(C122:C127)</f>
+        <v>18.725227295347171</v>
       </c>
       <c r="D129">
-        <f t="shared" si="30"/>
-        <v>8.2124783790462068</v>
+        <f t="shared" si="36"/>
+        <v>7.079145045712874</v>
       </c>
       <c r="E129">
-        <f t="shared" si="30"/>
-        <v>15.984580834378093</v>
+        <f t="shared" si="36"/>
+        <v>15.457449051432357</v>
       </c>
       <c r="F129">
-        <f t="shared" si="30"/>
-        <v>7.7601945611965801</v>
+        <f t="shared" si="36"/>
+        <v>10.593527894529913</v>
       </c>
       <c r="G129">
-        <f t="shared" si="30"/>
-        <v>84.364532019704441</v>
-      </c>
-    </row>
-    <row r="132" spans="1:7" x14ac:dyDescent="0.25">
+        <f t="shared" si="36"/>
+        <v>44.293103448275865</v>
+      </c>
+    </row>
+    <row r="132" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A132" t="s">
         <v>72</v>
       </c>
       <c r="B132" t="s">
+        <v>80</v>
+      </c>
+      <c r="C132" t="s">
         <v>0</v>
       </c>
-      <c r="C132" t="s">
+      <c r="D132" t="s">
         <v>2</v>
       </c>
-      <c r="D132" t="s">
+      <c r="E132" t="s">
         <v>63</v>
       </c>
-      <c r="E132" t="s">
+      <c r="F132" t="s">
         <v>64</v>
       </c>
-      <c r="F132" t="s">
+      <c r="G132" t="s">
         <v>65</v>
       </c>
-      <c r="G132" t="s">
+      <c r="H132" t="s">
         <v>66</v>
       </c>
     </row>
-    <row r="133" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A133" t="s">
         <v>75</v>
       </c>
-      <c r="B133" s="6">
-        <v>1.9618373652173864</v>
+      <c r="B133" t="s">
+        <v>54</v>
       </c>
       <c r="C133" s="6">
-        <v>1.8638160642219139</v>
+        <v>2.5235086214445861</v>
       </c>
       <c r="D133" s="6">
-        <v>-1.4804792761735253</v>
+        <v>2.4837340344014081</v>
       </c>
       <c r="E133" s="6">
-        <v>-1.9063449339704606</v>
+        <v>-1.9626479249720317</v>
       </c>
       <c r="F133" s="6">
-        <v>0.2781595461795463</v>
+        <v>-2.5142178213244453</v>
       </c>
       <c r="G133" s="6">
-        <v>-1.4450727642986172</v>
-      </c>
-    </row>
-    <row r="134" spans="1:7" x14ac:dyDescent="0.25">
+        <v>0.3872519972059611</v>
+      </c>
+      <c r="H133" s="6">
+        <v>-1.7510657252129647</v>
+      </c>
+    </row>
+    <row r="134" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A134" t="s">
         <v>55</v>
       </c>
-      <c r="B134" s="6">
-        <v>2.0599309473915355</v>
+      <c r="B134" t="s">
+        <v>55</v>
       </c>
       <c r="C134" s="6">
-        <v>-0.32520331562826899</v>
+        <v>2.2529248162725399</v>
       </c>
       <c r="D134" s="6">
-        <v>-0.28122049591070247</v>
+        <v>-0.36847603576441651</v>
       </c>
       <c r="E134" s="6">
-        <v>-1.124591429076774</v>
+        <v>-0.31698541664525309</v>
       </c>
       <c r="F134" s="6">
-        <v>0.10803395392536067</v>
+        <v>-1.2610968203770836</v>
       </c>
       <c r="G134" s="6">
-        <v>-0.4537426064865151</v>
-      </c>
-    </row>
-    <row r="135" spans="1:7" x14ac:dyDescent="0.25">
+        <v>0.127882822748078</v>
+      </c>
+      <c r="H134" s="6">
+        <v>-0.46749238244065189</v>
+      </c>
+    </row>
+    <row r="135" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A135" t="s">
         <v>56</v>
       </c>
-      <c r="B135" s="6">
-        <v>-2.5144140724136825</v>
+      <c r="B135" t="s">
+        <v>56</v>
       </c>
       <c r="C135" s="6">
-        <v>-2.6968376909718406</v>
+        <v>-3.7840503796027849</v>
       </c>
       <c r="D135" s="6">
-        <v>1.5090452457392198</v>
+        <v>-4.2047014761183785</v>
       </c>
       <c r="E135" s="6">
-        <v>2.630416288204521</v>
+        <v>2.3405646884596703</v>
       </c>
       <c r="F135" s="6">
-        <v>1.1358580636156261</v>
+        <v>4.0588613969278144</v>
       </c>
       <c r="G135" s="6">
-        <v>-1.3057059983618879</v>
-      </c>
-    </row>
-    <row r="136" spans="1:7" x14ac:dyDescent="0.25">
+        <v>1.8501293079477246</v>
+      </c>
+      <c r="H135" s="6">
+        <v>-1.851128004510501</v>
+      </c>
+    </row>
+    <row r="136" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A136" t="s">
         <v>76</v>
       </c>
-      <c r="B136" s="6">
-        <v>-0.53432394632818636</v>
+      <c r="B136" t="s">
+        <v>57</v>
       </c>
       <c r="C136" s="6">
-        <v>0.90989553650910848</v>
+        <v>-0.82704502425821391</v>
       </c>
       <c r="D136" s="6">
-        <v>1.0184571183711095</v>
+        <v>0.68160318812038334</v>
       </c>
       <c r="E136" s="6">
-        <v>0.10569725930559894</v>
+        <v>0.80384127743952682</v>
       </c>
       <c r="F136" s="6">
-        <v>-2.3577157439801271</v>
+        <v>-0.18806779145509095</v>
       </c>
       <c r="G136" s="6">
-        <v>3.0313488136887345</v>
-      </c>
-    </row>
-    <row r="137" spans="1:7" x14ac:dyDescent="0.25">
+        <v>-3.0998341830841243</v>
+      </c>
+      <c r="H136" s="6">
+        <v>6.7451483555328728</v>
+      </c>
+    </row>
+    <row r="137" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A137" t="s">
         <v>77</v>
       </c>
-      <c r="B137" s="6">
-        <v>2.0735297325689674</v>
+      <c r="B137" t="s">
+        <v>58</v>
       </c>
       <c r="C137" s="6">
-        <v>2.7092446872489253</v>
+        <v>2.3291005409264507</v>
       </c>
       <c r="D137" s="6">
-        <v>-1.3677717455369998</v>
+        <v>3.1527275832000812</v>
       </c>
       <c r="E137" s="6">
-        <v>-1.8527744356083116</v>
+        <v>-1.5833972023830365</v>
       </c>
       <c r="F137" s="6">
-        <v>-0.90492289666932879</v>
+        <v>-2.133831606720658</v>
       </c>
       <c r="G137" s="6">
-        <v>-0.74754500159640203</v>
-      </c>
-    </row>
-    <row r="138" spans="1:7" x14ac:dyDescent="0.25">
+        <v>-1.1001387253853605</v>
+      </c>
+      <c r="H137" s="6">
+        <v>-0.79101779136571349</v>
+      </c>
+    </row>
+    <row r="138" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A138" t="s">
         <v>78</v>
       </c>
-      <c r="B138" s="6">
-        <v>-0.74472937953292517</v>
+      <c r="B138" t="s">
+        <v>79</v>
       </c>
       <c r="C138" s="6">
-        <v>-0.88877216787349644</v>
+        <v>-0.40206321858408139</v>
       </c>
       <c r="D138" s="6">
-        <v>-0.86965655347867254</v>
+        <v>-0.49710319088589316</v>
       </c>
       <c r="E138" s="6">
-        <v>-0.85011121368339337</v>
+        <v>-0.48388471959081264</v>
       </c>
       <c r="F138" s="6">
-        <v>-5.7166195047502949E-2</v>
+        <v>-0.47057757527813282</v>
       </c>
       <c r="G138" s="6">
-        <v>8.4034306719829317</v>
+        <v>1.670179139828603</v>
+      </c>
+      <c r="H138" s="6">
+        <v>-0.17444452181248013</v>
       </c>
     </row>
   </sheetData>
@@ -6334,4 +6730,1255 @@
     <tablePart r:id="rId10"/>
   </tableParts>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7FA8DE67-3B52-43EA-968F-4153E5B0E745}">
+  <dimension ref="A1:R34"/>
+  <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="3" width="17.7109375" customWidth="1"/>
+    <col min="5" max="7" width="11.7109375" customWidth="1"/>
+    <col min="8" max="9" width="17.7109375" customWidth="1"/>
+    <col min="11" max="11" width="17.7109375" customWidth="1"/>
+    <col min="12" max="13" width="9.7109375" customWidth="1"/>
+    <col min="14" max="16" width="12.7109375" customWidth="1"/>
+    <col min="17" max="18" width="9.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:18" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="7" t="s">
+        <v>81</v>
+      </c>
+      <c r="B1" s="8" t="s">
+        <v>82</v>
+      </c>
+      <c r="C1" s="9" t="s">
+        <v>83</v>
+      </c>
+      <c r="E1" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="F1" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="G1" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="H1" s="8" t="s">
+        <v>83</v>
+      </c>
+      <c r="I1" s="9" t="s">
+        <v>23</v>
+      </c>
+      <c r="K1" s="7" t="s">
+        <v>85</v>
+      </c>
+      <c r="L1" s="8" t="s">
+        <v>0</v>
+      </c>
+      <c r="M1" s="8" t="s">
+        <v>2</v>
+      </c>
+      <c r="N1" s="8" t="s">
+        <v>63</v>
+      </c>
+      <c r="O1" s="8" t="s">
+        <v>64</v>
+      </c>
+      <c r="P1" s="8" t="s">
+        <v>65</v>
+      </c>
+      <c r="Q1" s="8" t="s">
+        <v>66</v>
+      </c>
+      <c r="R1" s="9" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="2" spans="1:18" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A2" s="10" t="s">
+        <v>4</v>
+      </c>
+      <c r="B2" s="11">
+        <v>118</v>
+      </c>
+      <c r="C2" s="12">
+        <v>9.3100000000000002E-2</v>
+      </c>
+      <c r="E2" s="16">
+        <v>1</v>
+      </c>
+      <c r="F2" s="17" t="s">
+        <v>24</v>
+      </c>
+      <c r="G2" s="11">
+        <v>44</v>
+      </c>
+      <c r="H2" s="11">
+        <v>3.47</v>
+      </c>
+      <c r="I2" s="18" t="s">
+        <v>25</v>
+      </c>
+      <c r="K2" s="10" t="s">
+        <v>4</v>
+      </c>
+      <c r="L2" s="11">
+        <v>58</v>
+      </c>
+      <c r="M2" s="11">
+        <v>14</v>
+      </c>
+      <c r="N2" s="11">
+        <v>8</v>
+      </c>
+      <c r="O2" s="11">
+        <v>7</v>
+      </c>
+      <c r="P2" s="11">
+        <v>21</v>
+      </c>
+      <c r="Q2" s="11">
+        <v>10</v>
+      </c>
+      <c r="R2" s="23">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="3" spans="1:18" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A3" s="13" t="s">
+        <v>29</v>
+      </c>
+      <c r="B3" s="14">
+        <v>349</v>
+      </c>
+      <c r="C3" s="15">
+        <v>0.27550000000000002</v>
+      </c>
+      <c r="E3" s="19">
+        <v>2</v>
+      </c>
+      <c r="F3" s="20" t="s">
+        <v>26</v>
+      </c>
+      <c r="G3" s="14">
+        <v>26</v>
+      </c>
+      <c r="H3" s="14">
+        <v>2.0499999999999998</v>
+      </c>
+      <c r="I3" s="21" t="s">
+        <v>27</v>
+      </c>
+      <c r="K3" s="13" t="s">
+        <v>29</v>
+      </c>
+      <c r="L3" s="14">
+        <v>115</v>
+      </c>
+      <c r="M3" s="14">
+        <v>72</v>
+      </c>
+      <c r="N3" s="14">
+        <v>28</v>
+      </c>
+      <c r="O3" s="14">
+        <v>52</v>
+      </c>
+      <c r="P3" s="14">
+        <v>65</v>
+      </c>
+      <c r="Q3" s="14">
+        <v>17</v>
+      </c>
+      <c r="R3" s="24">
+        <v>349</v>
+      </c>
+    </row>
+    <row r="4" spans="1:18" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A4" s="10" t="s">
+        <v>6</v>
+      </c>
+      <c r="B4" s="11">
+        <v>238</v>
+      </c>
+      <c r="C4" s="12">
+        <v>0.18779999999999999</v>
+      </c>
+      <c r="E4" s="16">
+        <v>3</v>
+      </c>
+      <c r="F4" s="17" t="s">
+        <v>28</v>
+      </c>
+      <c r="G4" s="11">
+        <v>23</v>
+      </c>
+      <c r="H4" s="11">
+        <v>1.82</v>
+      </c>
+      <c r="I4" s="18" t="s">
+        <v>29</v>
+      </c>
+      <c r="K4" s="10" t="s">
+        <v>6</v>
+      </c>
+      <c r="L4" s="11">
+        <v>33</v>
+      </c>
+      <c r="M4" s="11">
+        <v>47</v>
+      </c>
+      <c r="N4" s="11">
+        <v>45</v>
+      </c>
+      <c r="O4" s="11">
+        <v>43</v>
+      </c>
+      <c r="P4" s="11">
+        <v>63</v>
+      </c>
+      <c r="Q4" s="11">
+        <v>7</v>
+      </c>
+      <c r="R4" s="23">
+        <v>238</v>
+      </c>
+    </row>
+    <row r="5" spans="1:18" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A5" s="13" t="s">
+        <v>27</v>
+      </c>
+      <c r="B5" s="14">
+        <v>139</v>
+      </c>
+      <c r="C5" s="15">
+        <v>0.10970000000000001</v>
+      </c>
+      <c r="E5" s="19">
+        <v>4</v>
+      </c>
+      <c r="F5" s="20" t="s">
+        <v>30</v>
+      </c>
+      <c r="G5" s="14">
+        <v>18</v>
+      </c>
+      <c r="H5" s="14">
+        <v>1.42</v>
+      </c>
+      <c r="I5" s="21" t="s">
+        <v>6</v>
+      </c>
+      <c r="K5" s="13" t="s">
+        <v>27</v>
+      </c>
+      <c r="L5" s="14">
+        <v>36</v>
+      </c>
+      <c r="M5" s="14">
+        <v>36</v>
+      </c>
+      <c r="N5" s="14">
+        <v>26</v>
+      </c>
+      <c r="O5" s="14">
+        <v>9</v>
+      </c>
+      <c r="P5" s="14">
+        <v>24</v>
+      </c>
+      <c r="Q5" s="14">
+        <v>8</v>
+      </c>
+      <c r="R5" s="24">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="6" spans="1:18" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A6" s="10" t="s">
+        <v>37</v>
+      </c>
+      <c r="B6" s="11">
+        <v>131</v>
+      </c>
+      <c r="C6" s="12">
+        <v>0.10340000000000001</v>
+      </c>
+      <c r="E6" s="16">
+        <v>5</v>
+      </c>
+      <c r="F6" s="17" t="s">
+        <v>31</v>
+      </c>
+      <c r="G6" s="11">
+        <v>16</v>
+      </c>
+      <c r="H6" s="11">
+        <v>1.26</v>
+      </c>
+      <c r="I6" s="18" t="s">
+        <v>27</v>
+      </c>
+      <c r="K6" s="10" t="s">
+        <v>37</v>
+      </c>
+      <c r="L6" s="11">
+        <v>48</v>
+      </c>
+      <c r="M6" s="11">
+        <v>21</v>
+      </c>
+      <c r="N6" s="11">
+        <v>20</v>
+      </c>
+      <c r="O6" s="11">
+        <v>5</v>
+      </c>
+      <c r="P6" s="11">
+        <v>28</v>
+      </c>
+      <c r="Q6" s="11">
+        <v>9</v>
+      </c>
+      <c r="R6" s="23">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="7" spans="1:18" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A7" s="13" t="s">
+        <v>9</v>
+      </c>
+      <c r="B7" s="14">
+        <v>114</v>
+      </c>
+      <c r="C7" s="15">
+        <v>0.09</v>
+      </c>
+      <c r="E7" s="19">
+        <v>6</v>
+      </c>
+      <c r="F7" s="20" t="s">
+        <v>32</v>
+      </c>
+      <c r="G7" s="14">
+        <v>16</v>
+      </c>
+      <c r="H7" s="14">
+        <v>1.26</v>
+      </c>
+      <c r="I7" s="21" t="s">
+        <v>4</v>
+      </c>
+      <c r="K7" s="13" t="s">
+        <v>9</v>
+      </c>
+      <c r="L7" s="14">
+        <v>10</v>
+      </c>
+      <c r="M7" s="14">
+        <v>27</v>
+      </c>
+      <c r="N7" s="14">
+        <v>16</v>
+      </c>
+      <c r="O7" s="14">
+        <v>55</v>
+      </c>
+      <c r="P7" s="14">
+        <v>4</v>
+      </c>
+      <c r="Q7" s="14">
+        <v>2</v>
+      </c>
+      <c r="R7" s="24">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="8" spans="1:18" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A8" s="10" t="s">
+        <v>25</v>
+      </c>
+      <c r="B8" s="11">
+        <v>178</v>
+      </c>
+      <c r="C8" s="12">
+        <v>0.14050000000000001</v>
+      </c>
+      <c r="E8" s="16">
+        <v>7</v>
+      </c>
+      <c r="F8" s="17" t="s">
+        <v>33</v>
+      </c>
+      <c r="G8" s="11">
+        <v>16</v>
+      </c>
+      <c r="H8" s="11">
+        <v>1.26</v>
+      </c>
+      <c r="I8" s="18" t="s">
+        <v>27</v>
+      </c>
+      <c r="K8" s="10" t="s">
+        <v>25</v>
+      </c>
+      <c r="L8" s="11">
+        <v>50</v>
+      </c>
+      <c r="M8" s="11">
+        <v>28</v>
+      </c>
+      <c r="N8" s="11">
+        <v>17</v>
+      </c>
+      <c r="O8" s="11">
+        <v>45</v>
+      </c>
+      <c r="P8" s="11">
+        <v>32</v>
+      </c>
+      <c r="Q8" s="11">
+        <v>6</v>
+      </c>
+      <c r="R8" s="23">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="9" spans="1:18" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="E9" s="19">
+        <v>8</v>
+      </c>
+      <c r="F9" s="20" t="s">
+        <v>34</v>
+      </c>
+      <c r="G9" s="14">
+        <v>15</v>
+      </c>
+      <c r="H9" s="14">
+        <v>1.18</v>
+      </c>
+      <c r="I9" s="21" t="s">
+        <v>4</v>
+      </c>
+      <c r="K9" s="13" t="s">
+        <v>60</v>
+      </c>
+      <c r="L9" s="14">
+        <v>350</v>
+      </c>
+      <c r="M9" s="14">
+        <v>245</v>
+      </c>
+      <c r="N9" s="14">
+        <v>160</v>
+      </c>
+      <c r="O9" s="14">
+        <v>216</v>
+      </c>
+      <c r="P9" s="14">
+        <v>237</v>
+      </c>
+      <c r="Q9" s="14">
+        <v>59</v>
+      </c>
+      <c r="R9" s="24">
+        <v>1267</v>
+      </c>
+    </row>
+    <row r="10" spans="1:18" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A10" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="B10" s="8" t="s">
+        <v>82</v>
+      </c>
+      <c r="C10" s="9" t="s">
+        <v>83</v>
+      </c>
+      <c r="E10" s="16">
+        <v>9</v>
+      </c>
+      <c r="F10" s="17" t="s">
+        <v>35</v>
+      </c>
+      <c r="G10" s="11">
+        <v>15</v>
+      </c>
+      <c r="H10" s="11">
+        <v>1.18</v>
+      </c>
+      <c r="I10" s="18" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="11" spans="1:18" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A11" s="10" t="s">
+        <v>50</v>
+      </c>
+      <c r="B11" s="11">
+        <v>143</v>
+      </c>
+      <c r="C11" s="12">
+        <v>0.40970000000000001</v>
+      </c>
+      <c r="E11" s="19">
+        <v>10</v>
+      </c>
+      <c r="F11" s="20" t="s">
+        <v>36</v>
+      </c>
+      <c r="G11" s="14">
+        <v>14</v>
+      </c>
+      <c r="H11" s="14">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="I11" s="21" t="s">
+        <v>37</v>
+      </c>
+      <c r="K11" s="7" t="s">
+        <v>72</v>
+      </c>
+      <c r="L11" s="8" t="s">
+        <v>0</v>
+      </c>
+      <c r="M11" s="8" t="s">
+        <v>2</v>
+      </c>
+      <c r="N11" s="8" t="s">
+        <v>63</v>
+      </c>
+      <c r="O11" s="8" t="s">
+        <v>64</v>
+      </c>
+      <c r="P11" s="8" t="s">
+        <v>65</v>
+      </c>
+      <c r="Q11" s="9" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="12" spans="1:18" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A12" s="13" t="s">
+        <v>49</v>
+      </c>
+      <c r="B12" s="14">
+        <v>112</v>
+      </c>
+      <c r="C12" s="15">
+        <v>0.32090000000000002</v>
+      </c>
+      <c r="E12" s="16">
+        <v>11</v>
+      </c>
+      <c r="F12" s="17" t="s">
+        <v>38</v>
+      </c>
+      <c r="G12" s="11">
+        <v>14</v>
+      </c>
+      <c r="H12" s="11">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="I12" s="18" t="s">
+        <v>37</v>
+      </c>
+      <c r="K12" s="10" t="s">
+        <v>4</v>
+      </c>
+      <c r="L12" s="25">
+        <v>5.4920642134221636</v>
+      </c>
+      <c r="M12" s="25">
+        <v>-2.1582896415477171</v>
+      </c>
+      <c r="N12" s="25">
+        <v>-2.0084620800211743</v>
+      </c>
+      <c r="O12" s="25">
+        <v>-3.3718165941885085</v>
+      </c>
+      <c r="P12" s="25">
+        <v>-0.2658973204616274</v>
+      </c>
+      <c r="Q12" s="26">
+        <v>2.0668634289343135</v>
+      </c>
+    </row>
+    <row r="13" spans="1:18" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A13" s="10" t="s">
+        <v>86</v>
+      </c>
+      <c r="B13" s="11">
+        <v>36</v>
+      </c>
+      <c r="C13" s="12">
+        <v>0.1032</v>
+      </c>
+      <c r="E13" s="19">
+        <v>12</v>
+      </c>
+      <c r="F13" s="20" t="s">
+        <v>39</v>
+      </c>
+      <c r="G13" s="14">
+        <v>13</v>
+      </c>
+      <c r="H13" s="14">
+        <v>1.03</v>
+      </c>
+      <c r="I13" s="21" t="s">
+        <v>4</v>
+      </c>
+      <c r="K13" s="13" t="s">
+        <v>29</v>
+      </c>
+      <c r="L13" s="27">
+        <v>2.6146807645880816</v>
+      </c>
+      <c r="M13" s="27">
+        <v>0.71873014400110835</v>
+      </c>
+      <c r="N13" s="27">
+        <v>-3.0428709913576326</v>
+      </c>
+      <c r="O13" s="27">
+        <v>-1.2538616661581017</v>
+      </c>
+      <c r="P13" s="27">
+        <v>-4.5566376539646403E-2</v>
+      </c>
+      <c r="Q13" s="28">
+        <v>0.22330740138774252</v>
+      </c>
+    </row>
+    <row r="14" spans="1:18" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A14" s="13" t="s">
+        <v>74</v>
+      </c>
+      <c r="B14" s="14">
+        <v>35</v>
+      </c>
+      <c r="C14" s="15">
+        <v>0.1003</v>
+      </c>
+      <c r="E14" s="16">
+        <v>13</v>
+      </c>
+      <c r="F14" s="17" t="s">
+        <v>40</v>
+      </c>
+      <c r="G14" s="11">
+        <v>12</v>
+      </c>
+      <c r="H14" s="11">
+        <v>0.95</v>
+      </c>
+      <c r="I14" s="18" t="s">
+        <v>27</v>
+      </c>
+      <c r="K14" s="10" t="s">
+        <v>6</v>
+      </c>
+      <c r="L14" s="25">
+        <v>-5.2675227355524452</v>
+      </c>
+      <c r="M14" s="25">
+        <v>0.1780963249567569</v>
+      </c>
+      <c r="N14" s="25">
+        <v>3.2361127849020757</v>
+      </c>
+      <c r="O14" s="25">
+        <v>0.46390223854658152</v>
+      </c>
+      <c r="P14" s="25">
+        <v>3.4087371854024338</v>
+      </c>
+      <c r="Q14" s="26">
+        <v>-1.3937187636038388</v>
+      </c>
+    </row>
+    <row r="15" spans="1:18" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A15" s="10" t="s">
+        <v>48</v>
+      </c>
+      <c r="B15" s="11">
+        <v>23</v>
+      </c>
+      <c r="C15" s="12">
+        <v>6.59E-2</v>
+      </c>
+      <c r="E15" s="19">
+        <v>14</v>
+      </c>
+      <c r="F15" s="20" t="s">
+        <v>41</v>
+      </c>
+      <c r="G15" s="14">
+        <v>11</v>
+      </c>
+      <c r="H15" s="14">
+        <v>0.87</v>
+      </c>
+      <c r="I15" s="21" t="s">
+        <v>37</v>
+      </c>
+      <c r="K15" s="13" t="s">
+        <v>27</v>
+      </c>
+      <c r="L15" s="27">
+        <v>-0.48205371817383663</v>
+      </c>
+      <c r="M15" s="27">
+        <v>2.0761703315433313</v>
+      </c>
+      <c r="N15" s="27">
+        <v>2.2859014460205067</v>
+      </c>
+      <c r="O15" s="27">
+        <v>-3.5131858429096736</v>
+      </c>
+      <c r="P15" s="27">
+        <v>-0.46122361542787699</v>
+      </c>
+      <c r="Q15" s="28">
+        <v>0.65155015716761744</v>
+      </c>
+    </row>
+    <row r="16" spans="1:18" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="E16" s="16">
+        <v>15</v>
+      </c>
+      <c r="F16" s="17" t="s">
+        <v>42</v>
+      </c>
+      <c r="G16" s="11">
+        <v>11</v>
+      </c>
+      <c r="H16" s="11">
+        <v>0.87</v>
+      </c>
+      <c r="I16" s="18" t="s">
+        <v>9</v>
+      </c>
+      <c r="K16" s="10" t="s">
+        <v>37</v>
+      </c>
+      <c r="L16" s="25">
+        <v>2.4375332289575526</v>
+      </c>
+      <c r="M16" s="25">
+        <v>-1.0119734219963863</v>
+      </c>
+      <c r="N16" s="25">
+        <v>0.96029308745601505</v>
+      </c>
+      <c r="O16" s="25">
+        <v>-4.2529215553917403</v>
+      </c>
+      <c r="P16" s="25">
+        <v>0.8271349820637478</v>
+      </c>
+      <c r="Q16" s="26">
+        <v>1.2698229527821767</v>
+      </c>
+    </row>
+    <row r="17" spans="1:17" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A17" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="B17" s="8" t="s">
+        <v>82</v>
+      </c>
+      <c r="C17" s="9" t="s">
+        <v>83</v>
+      </c>
+      <c r="E17" s="19">
+        <v>16</v>
+      </c>
+      <c r="F17" s="20" t="s">
+        <v>43</v>
+      </c>
+      <c r="G17" s="14">
+        <v>11</v>
+      </c>
+      <c r="H17" s="14">
+        <v>0.87</v>
+      </c>
+      <c r="I17" s="21" t="s">
+        <v>6</v>
+      </c>
+      <c r="K17" s="13" t="s">
+        <v>9</v>
+      </c>
+      <c r="L17" s="27">
+        <v>-4.7190021961399848</v>
+      </c>
+      <c r="M17" s="27">
+        <v>1.2319787619535989</v>
+      </c>
+      <c r="N17" s="27">
+        <v>0.47403578732849494</v>
+      </c>
+      <c r="O17" s="27">
+        <v>9.2852546735458805</v>
+      </c>
+      <c r="P17" s="27">
+        <v>-4.3617720712734034</v>
+      </c>
+      <c r="Q17" s="28">
+        <v>-1.5416402093239689</v>
+      </c>
+    </row>
+    <row r="18" spans="1:17" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A18" s="10" t="s">
+        <v>56</v>
+      </c>
+      <c r="B18" s="11">
+        <v>116</v>
+      </c>
+      <c r="C18" s="12">
+        <v>0.4874</v>
+      </c>
+      <c r="E18" s="16">
+        <v>17</v>
+      </c>
+      <c r="F18" s="17" t="s">
+        <v>44</v>
+      </c>
+      <c r="G18" s="11">
+        <v>10</v>
+      </c>
+      <c r="H18" s="11">
+        <v>0.79</v>
+      </c>
+      <c r="I18" s="18" t="s">
+        <v>9</v>
+      </c>
+      <c r="K18" s="10" t="s">
+        <v>25</v>
+      </c>
+      <c r="L18" s="25">
+        <v>0.14984248799038094</v>
+      </c>
+      <c r="M18" s="25">
+        <v>-1.3141957076713142</v>
+      </c>
+      <c r="N18" s="25">
+        <v>-1.3333759239663781</v>
+      </c>
+      <c r="O18" s="25">
+        <v>3.1504882936300946</v>
+      </c>
+      <c r="P18" s="25">
+        <v>-0.26868581187039664</v>
+      </c>
+      <c r="Q18" s="26">
+        <v>-0.87821912668142776</v>
+      </c>
+    </row>
+    <row r="19" spans="1:17" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A19" s="13" t="s">
+        <v>75</v>
+      </c>
+      <c r="B19" s="14">
+        <v>71</v>
+      </c>
+      <c r="C19" s="15">
+        <v>0.29830000000000001</v>
+      </c>
+      <c r="E19" s="19">
+        <v>18</v>
+      </c>
+      <c r="F19" s="20" t="s">
+        <v>45</v>
+      </c>
+      <c r="G19" s="14">
+        <v>10</v>
+      </c>
+      <c r="H19" s="14">
+        <v>0.79</v>
+      </c>
+      <c r="I19" s="21" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="20" spans="1:17" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A20" s="10" t="s">
+        <v>76</v>
+      </c>
+      <c r="B20" s="11">
+        <v>24</v>
+      </c>
+      <c r="C20" s="12">
+        <v>0.1008</v>
+      </c>
+      <c r="E20" s="16">
+        <v>19</v>
+      </c>
+      <c r="F20" s="17" t="s">
+        <v>46</v>
+      </c>
+      <c r="G20" s="11">
+        <v>10</v>
+      </c>
+      <c r="H20" s="11">
+        <v>0.79</v>
+      </c>
+      <c r="I20" s="18" t="s">
+        <v>27</v>
+      </c>
+      <c r="K20" s="7" t="s">
+        <v>72</v>
+      </c>
+      <c r="L20" s="8" t="s">
+        <v>0</v>
+      </c>
+      <c r="M20" s="8" t="s">
+        <v>2</v>
+      </c>
+      <c r="N20" s="8" t="s">
+        <v>63</v>
+      </c>
+      <c r="O20" s="8" t="s">
+        <v>64</v>
+      </c>
+      <c r="P20" s="8" t="s">
+        <v>65</v>
+      </c>
+      <c r="Q20" s="9" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="21" spans="1:17" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A21" s="13" t="s">
+        <v>77</v>
+      </c>
+      <c r="B21" s="14">
+        <v>19</v>
+      </c>
+      <c r="C21" s="15">
+        <v>7.9799999999999996E-2</v>
+      </c>
+      <c r="E21" s="19">
+        <v>20</v>
+      </c>
+      <c r="F21" s="20" t="s">
+        <v>47</v>
+      </c>
+      <c r="G21" s="14">
+        <v>9</v>
+      </c>
+      <c r="H21" s="14">
+        <v>0.71</v>
+      </c>
+      <c r="I21" s="21" t="s">
+        <v>29</v>
+      </c>
+      <c r="K21" s="10" t="s">
+        <v>48</v>
+      </c>
+      <c r="L21" s="25">
+        <v>2.4883088180994499</v>
+      </c>
+      <c r="M21" s="25">
+        <v>2.2686124772108611</v>
+      </c>
+      <c r="N21" s="25">
+        <v>-1.4655287105051573</v>
+      </c>
+      <c r="O21" s="25">
+        <v>-2.0763056158551207</v>
+      </c>
+      <c r="P21" s="25">
+        <v>-1.8197375833118294</v>
+      </c>
+      <c r="Q21" s="26">
+        <v>-1.122853896195074</v>
+      </c>
+    </row>
+    <row r="22" spans="1:17" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A22" s="10" t="s">
+        <v>55</v>
+      </c>
+      <c r="B22" s="11">
+        <v>7</v>
+      </c>
+      <c r="C22" s="12">
+        <v>2.9399999999999999E-2</v>
+      </c>
+      <c r="K22" s="13" t="s">
+        <v>49</v>
+      </c>
+      <c r="L22" s="27">
+        <v>1.7307060849464544</v>
+      </c>
+      <c r="M22" s="27">
+        <v>0.53669167151937391</v>
+      </c>
+      <c r="N22" s="27">
+        <v>-1.6823839916205392</v>
+      </c>
+      <c r="O22" s="27">
+        <v>-1.5094993557334204</v>
+      </c>
+      <c r="P22" s="27">
+        <v>-0.54771972015889991</v>
+      </c>
+      <c r="Q22" s="28">
+        <v>0.8226683547258673</v>
+      </c>
+    </row>
+    <row r="23" spans="1:17" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A23" s="13" t="s">
+        <v>84</v>
+      </c>
+      <c r="B23" s="14">
+        <v>1</v>
+      </c>
+      <c r="C23" s="15">
+        <v>4.1999999999999997E-3</v>
+      </c>
+      <c r="K23" s="10" t="s">
+        <v>50</v>
+      </c>
+      <c r="L23" s="25">
+        <v>0.89840653026524542</v>
+      </c>
+      <c r="M23" s="25">
+        <v>0.13410785002587425</v>
+      </c>
+      <c r="N23" s="25">
+        <v>-0.18943642835292535</v>
+      </c>
+      <c r="O23" s="25">
+        <v>-2.8447703227133907</v>
+      </c>
+      <c r="P23" s="25">
+        <v>0.94131093284436518</v>
+      </c>
+      <c r="Q23" s="26">
+        <v>1.0286696599394156</v>
+      </c>
+    </row>
+    <row r="24" spans="1:17" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A24" s="22"/>
+      <c r="K24" s="13" t="s">
+        <v>51</v>
+      </c>
+      <c r="L24" s="27">
+        <v>-3.6926939207568199</v>
+      </c>
+      <c r="M24" s="27">
+        <v>-3.2301162957854803</v>
+      </c>
+      <c r="N24" s="27">
+        <v>3.9595754044599434</v>
+      </c>
+      <c r="O24" s="27">
+        <v>5.2567505085942825</v>
+      </c>
+      <c r="P24" s="27">
+        <v>1.0375426592668091</v>
+      </c>
+      <c r="Q24" s="28">
+        <v>-1.4336634516664148</v>
+      </c>
+    </row>
+    <row r="25" spans="1:17" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="K25" s="10" t="s">
+        <v>74</v>
+      </c>
+      <c r="L25" s="25">
+        <v>-2.476805283211045</v>
+      </c>
+      <c r="M25" s="25">
+        <v>0.34322320195023737</v>
+      </c>
+      <c r="N25" s="25">
+        <v>0.12593810034321021</v>
+      </c>
+      <c r="O25" s="25">
+        <v>3.3955933067103601</v>
+      </c>
+      <c r="P25" s="25">
+        <v>-0.23739774742805125</v>
+      </c>
+      <c r="Q25" s="26">
+        <v>-0.58351963166487852</v>
+      </c>
+    </row>
+    <row r="26" spans="1:17" ht="16.5" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="27" spans="1:17" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="K27" s="7" t="s">
+        <v>72</v>
+      </c>
+      <c r="L27" s="8" t="s">
+        <v>0</v>
+      </c>
+      <c r="M27" s="8" t="s">
+        <v>2</v>
+      </c>
+      <c r="N27" s="8" t="s">
+        <v>63</v>
+      </c>
+      <c r="O27" s="8" t="s">
+        <v>64</v>
+      </c>
+      <c r="P27" s="8" t="s">
+        <v>65</v>
+      </c>
+      <c r="Q27" s="9" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="28" spans="1:17" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="K28" s="10" t="s">
+        <v>75</v>
+      </c>
+      <c r="L28" s="25">
+        <v>2.5235086214445861</v>
+      </c>
+      <c r="M28" s="25">
+        <v>2.4837340344014081</v>
+      </c>
+      <c r="N28" s="25">
+        <v>-1.9626479249720317</v>
+      </c>
+      <c r="O28" s="25">
+        <v>-2.5142178213244453</v>
+      </c>
+      <c r="P28" s="25">
+        <v>0.3872519972059611</v>
+      </c>
+      <c r="Q28" s="26">
+        <v>-1.7510657252129647</v>
+      </c>
+    </row>
+    <row r="29" spans="1:17" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="K29" s="13" t="s">
+        <v>55</v>
+      </c>
+      <c r="L29" s="27">
+        <v>2.2529248162725399</v>
+      </c>
+      <c r="M29" s="27">
+        <v>-0.36847603576441651</v>
+      </c>
+      <c r="N29" s="27">
+        <v>-0.31698541664525309</v>
+      </c>
+      <c r="O29" s="27">
+        <v>-1.2610968203770836</v>
+      </c>
+      <c r="P29" s="27">
+        <v>0.127882822748078</v>
+      </c>
+      <c r="Q29" s="28">
+        <v>-0.46749238244065189</v>
+      </c>
+    </row>
+    <row r="30" spans="1:17" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="K30" s="10" t="s">
+        <v>56</v>
+      </c>
+      <c r="L30" s="25">
+        <v>-3.7840503796027849</v>
+      </c>
+      <c r="M30" s="25">
+        <v>-4.2047014761183785</v>
+      </c>
+      <c r="N30" s="25">
+        <v>2.3405646884596703</v>
+      </c>
+      <c r="O30" s="25">
+        <v>4.0588613969278144</v>
+      </c>
+      <c r="P30" s="25">
+        <v>1.8501293079477246</v>
+      </c>
+      <c r="Q30" s="26">
+        <v>-1.851128004510501</v>
+      </c>
+    </row>
+    <row r="31" spans="1:17" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="K31" s="13" t="s">
+        <v>76</v>
+      </c>
+      <c r="L31" s="27">
+        <v>-0.82704502425821391</v>
+      </c>
+      <c r="M31" s="27">
+        <v>0.68160318812038334</v>
+      </c>
+      <c r="N31" s="27">
+        <v>0.80384127743952682</v>
+      </c>
+      <c r="O31" s="27">
+        <v>-0.18806779145509095</v>
+      </c>
+      <c r="P31" s="27">
+        <v>-3.0998341830841243</v>
+      </c>
+      <c r="Q31" s="28">
+        <v>6.7451483555328728</v>
+      </c>
+    </row>
+    <row r="32" spans="1:17" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="K32" s="10" t="s">
+        <v>77</v>
+      </c>
+      <c r="L32" s="25">
+        <v>2.3291005409264507</v>
+      </c>
+      <c r="M32" s="25">
+        <v>3.1527275832000812</v>
+      </c>
+      <c r="N32" s="25">
+        <v>-1.5833972023830365</v>
+      </c>
+      <c r="O32" s="25">
+        <v>-2.133831606720658</v>
+      </c>
+      <c r="P32" s="25">
+        <v>-1.1001387253853605</v>
+      </c>
+      <c r="Q32" s="26">
+        <v>-0.79101779136571349</v>
+      </c>
+    </row>
+    <row r="33" spans="11:17" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="K33" s="13" t="s">
+        <v>84</v>
+      </c>
+      <c r="L33" s="27">
+        <v>-0.40206321858408139</v>
+      </c>
+      <c r="M33" s="27">
+        <v>-0.49710319088589316</v>
+      </c>
+      <c r="N33" s="27">
+        <v>-0.48388471959081264</v>
+      </c>
+      <c r="O33" s="27">
+        <v>-0.47057757527813282</v>
+      </c>
+      <c r="P33" s="27">
+        <v>1.670179139828603</v>
+      </c>
+      <c r="Q33" s="28">
+        <v>-0.17444452181248013</v>
+      </c>
+    </row>
+    <row r="34" spans="11:17" x14ac:dyDescent="0.25">
+      <c r="K34" s="22"/>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="2" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+</worksheet>
 </file>